--- a/public/exports-from-60/29188327.xlsx
+++ b/public/exports-from-60/29188327.xlsx
@@ -59,7 +59,7 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Areal (m²)</t>
+          <t xml:space="preserve">Opvarmet BBR-areal (m²)</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
@@ -4639,7 +4639,7 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t xml:space="preserve">311219391</t>
+          <t xml:space="preserve">311219392</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">

--- a/public/exports-from-60/29188327.xlsx
+++ b/public/exports-from-60/29188327.xlsx
@@ -1766,7 +1766,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stavnsholtvej 171A</t>
+          <t xml:space="preserve">Stavnsholtvej 35A</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1776,16 +1776,16 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t xml:space="preserve">8483114</t>
+          <t xml:space="preserve">717746, 2265705</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J24">
-        <v>542</v>
+        <v>163</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stavnsholtvej 35A</t>
+          <t xml:space="preserve">Stavnsholtvej 35B</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1856,11 +1856,11 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J25">
-        <v>163</v>
+        <v>180</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
@@ -1916,7 +1916,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stavnsholtvej 35B</t>
+          <t xml:space="preserve">Stavnsholtvej 49C</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1926,16 +1926,16 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t xml:space="preserve">717746, 2265705</t>
+          <t xml:space="preserve">717751, 10165819</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J26">
-        <v>180</v>
+        <v>124</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -1991,7 +1991,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stavnsholtvej 49C</t>
+          <t xml:space="preserve">Stavnsholtvej 49D</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -2001,16 +2001,16 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t xml:space="preserve">717751, 10165819</t>
+          <t xml:space="preserve">2266340</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J27">
-        <v>124</v>
+        <v>112</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
@@ -2066,7 +2066,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stavnsholtvej 49D</t>
+          <t xml:space="preserve">Stavnsholtvej 49E</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -2076,16 +2076,16 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t xml:space="preserve">2266340</t>
+          <t xml:space="preserve">717749, 2266339</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J28">
-        <v>112</v>
+        <v>175</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -2141,26 +2141,26 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stavnsholtvej 49E</t>
+          <t xml:space="preserve">Stiager 8</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t xml:space="preserve">3520</t>
+          <t xml:space="preserve">3500</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t xml:space="preserve">717749, 2266339</t>
+          <t xml:space="preserve">2138514</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J29">
-        <v>175</v>
+        <v>1928</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
@@ -2231,11 +2231,11 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J30">
-        <v>1928</v>
+        <v>5224</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
@@ -2291,45 +2291,45 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stiager 8</t>
+          <t xml:space="preserve">Ryttergårdsvej 135</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t xml:space="preserve">3500</t>
+          <t xml:space="preserve">3520</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t xml:space="preserve">2138514</t>
+          <t xml:space="preserve">8396261</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J31">
-        <v>5224</v>
+        <v>586</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">311181115</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Sweco Danmark A/S</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2026-06-06</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
@@ -2366,40 +2366,40 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ryttergårdsvej 135</t>
+          <t xml:space="preserve">Kirke Værløsevej 58</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t xml:space="preserve">3520</t>
+          <t xml:space="preserve">3500</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t xml:space="preserve">8396261</t>
+          <t xml:space="preserve">2136995</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J32">
-        <v>586</v>
+        <v>1779</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t xml:space="preserve">311181115</t>
+          <t xml:space="preserve">311184981</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sweco Danmark A/S</t>
+          <t xml:space="preserve">factum2 as</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-06</t>
+          <t xml:space="preserve">2026-06-22</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -2441,40 +2441,40 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirke Værløsevej 58</t>
+          <t xml:space="preserve">Stavnsholtvej 43</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t xml:space="preserve">3500</t>
+          <t xml:space="preserve">3520</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t xml:space="preserve">2136995</t>
+          <t xml:space="preserve">7966736</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J33">
-        <v>1779</v>
+        <v>9410</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t xml:space="preserve">311184981</t>
+          <t xml:space="preserve">311201630</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t xml:space="preserve">factum2 as</t>
+          <t xml:space="preserve">Sweco Danmark A/S</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-22</t>
+          <t xml:space="preserve">2026-09-20</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stavnsholtvej 43</t>
+          <t xml:space="preserve">Birkhøjterrasserne 2A</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -2526,20 +2526,20 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t xml:space="preserve">7966736</t>
+          <t xml:space="preserve">2263252</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J34">
-        <v>9410</v>
+        <v>827</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t xml:space="preserve">311201630</t>
+          <t xml:space="preserve">311207684</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -2549,7 +2549,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-20</t>
+          <t xml:space="preserve">2026-10-20</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -2591,30 +2591,30 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Birkhøjterrasserne 2A</t>
+          <t xml:space="preserve">Bymidten 118</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t xml:space="preserve">3520</t>
+          <t xml:space="preserve">3500</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t xml:space="preserve">2263252</t>
+          <t xml:space="preserve">2138693</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J35">
-        <v>827</v>
+        <v>400</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t xml:space="preserve">311207684</t>
+          <t xml:space="preserve">311207704</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -2666,17 +2666,17 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bymidten 118</t>
+          <t xml:space="preserve">Farum Park 2</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t xml:space="preserve">3500</t>
+          <t xml:space="preserve">3520</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t xml:space="preserve">2138693</t>
+          <t xml:space="preserve">2262667</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2685,11 +2685,11 @@
         </is>
       </c>
       <c r="J36">
-        <v>400</v>
+        <v>2420</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t xml:space="preserve">311207704</t>
+          <t xml:space="preserve">311207663</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -2756,11 +2756,11 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J37">
-        <v>2420</v>
+        <v>3278</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
@@ -2816,30 +2816,30 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Farum Park 2</t>
+          <t xml:space="preserve">Højeloft Vænge 46</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t xml:space="preserve">3520</t>
+          <t xml:space="preserve">3500</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t xml:space="preserve">2262667</t>
+          <t xml:space="preserve">2138085</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J38">
-        <v>3278</v>
+        <v>473</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t xml:space="preserve">311207663</t>
+          <t xml:space="preserve">311207728</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -2891,7 +2891,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Højeloft Vænge 46</t>
+          <t xml:space="preserve">Jonstrupvangvej 140</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t xml:space="preserve">2138085</t>
+          <t xml:space="preserve">8090892</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2910,11 +2910,11 @@
         </is>
       </c>
       <c r="J39">
-        <v>473</v>
+        <v>396</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t xml:space="preserve">311207728</t>
+          <t xml:space="preserve">311207677</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -2966,7 +2966,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jonstrupvangvej 140</t>
+          <t xml:space="preserve">Kirke Værløsevej 36A</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t xml:space="preserve">8090892</t>
+          <t xml:space="preserve">2136011</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2985,11 +2985,11 @@
         </is>
       </c>
       <c r="J40">
-        <v>396</v>
+        <v>878</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t xml:space="preserve">311207677</t>
+          <t xml:space="preserve">311208376</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -2999,7 +2999,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-20</t>
+          <t xml:space="preserve">2026-10-25</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -3041,17 +3041,17 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stavnsholtvej 168</t>
+          <t xml:space="preserve">Kirke Værløsevej 36B</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t xml:space="preserve">3520</t>
+          <t xml:space="preserve">3500</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t xml:space="preserve">2266105</t>
+          <t xml:space="preserve">2136011</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -3060,11 +3060,11 @@
         </is>
       </c>
       <c r="J41">
-        <v>867</v>
+        <v>532</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t xml:space="preserve">311207687</t>
+          <t xml:space="preserve">311208376</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -3074,7 +3074,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-20</t>
+          <t xml:space="preserve">2026-10-25</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -3116,7 +3116,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stavnsholtvej 180</t>
+          <t xml:space="preserve">Birkhøjterrasserne 1</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -3126,7 +3126,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t xml:space="preserve">2266105</t>
+          <t xml:space="preserve">2263252</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -3135,11 +3135,11 @@
         </is>
       </c>
       <c r="J42">
-        <v>309</v>
+        <v>112</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t xml:space="preserve">311207711</t>
+          <t xml:space="preserve">311208638</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -3149,7 +3149,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-20</t>
+          <t xml:space="preserve">2026-10-26</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirke Værløsevej 36A</t>
+          <t xml:space="preserve">Ny Vestergårdsvej 9</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -3201,20 +3201,20 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t xml:space="preserve">2136011</t>
+          <t xml:space="preserve">2135988</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J43">
-        <v>878</v>
+        <v>1413</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t xml:space="preserve">311208376</t>
+          <t xml:space="preserve">311210314</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -3224,7 +3224,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-25</t>
+          <t xml:space="preserve">2026-11-03</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -3266,7 +3266,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirke Værløsevej 36B</t>
+          <t xml:space="preserve">Kirke Værløsevej 48C</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -3276,30 +3276,30 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t xml:space="preserve">2136011</t>
+          <t xml:space="preserve">2138121</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J44">
-        <v>532</v>
+        <v>170</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t xml:space="preserve">311208376</t>
+          <t xml:space="preserve">311216946</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sweco Danmark A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-25</t>
+          <t xml:space="preserve">2026-12-09</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -3341,7 +3341,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirke Værløsevej 62</t>
+          <t xml:space="preserve">Kirke Værløsevej 48F</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -3351,30 +3351,30 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t xml:space="preserve">8736262</t>
+          <t xml:space="preserve">2138262</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J45">
-        <v>213</v>
+        <v>126</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t xml:space="preserve">311208388</t>
+          <t xml:space="preserve">311219398</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sweco Danmark A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-25</t>
+          <t xml:space="preserve">2026-12-22</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -3416,40 +3416,40 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirke Værløsevej 62</t>
+          <t xml:space="preserve">Kulturtorvet 6</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t xml:space="preserve">3500</t>
+          <t xml:space="preserve">3520</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t xml:space="preserve">8736262</t>
+          <t xml:space="preserve">2263807</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J46">
-        <v>356</v>
+        <v>7375</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t xml:space="preserve">311208392</t>
+          <t xml:space="preserve">311219413</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sweco Danmark A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-25</t>
+          <t xml:space="preserve">2026-12-22</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirke Værløsevej 62</t>
+          <t xml:space="preserve">Solbjerghaven 4</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -3501,20 +3501,20 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t xml:space="preserve">8736262</t>
+          <t xml:space="preserve">8234925</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J47">
-        <v>293</v>
+        <v>601</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t xml:space="preserve">311208394</t>
+          <t xml:space="preserve">311219403</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -3524,7 +3524,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-25</t>
+          <t xml:space="preserve">2026-12-22</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirke Værløsevej 62</t>
+          <t xml:space="preserve">Solbjerghaven 4</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -3576,20 +3576,20 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t xml:space="preserve">8736262</t>
+          <t xml:space="preserve">8234925</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J48">
-        <v>245</v>
+        <v>376</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t xml:space="preserve">311208390</t>
+          <t xml:space="preserve">311219403</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-25</t>
+          <t xml:space="preserve">2026-12-22</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -3641,30 +3641,30 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Birkhøjterrasserne 1</t>
+          <t xml:space="preserve">Solbjerghaven 4</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t xml:space="preserve">3520</t>
+          <t xml:space="preserve">3500</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t xml:space="preserve">2263252</t>
+          <t xml:space="preserve">8234925</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J49">
-        <v>112</v>
+        <v>376</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t xml:space="preserve">311208638</t>
+          <t xml:space="preserve">311219403</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -3674,7 +3674,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-26</t>
+          <t xml:space="preserve">2026-12-22</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ny Vestergårdsvej 9</t>
+          <t xml:space="preserve">Solbjerghaven 4</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -3726,20 +3726,20 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t xml:space="preserve">2135988</t>
+          <t xml:space="preserve">8234925</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J50">
-        <v>1413</v>
+        <v>486</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t xml:space="preserve">311210314</t>
+          <t xml:space="preserve">311219403</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -3749,7 +3749,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-03</t>
+          <t xml:space="preserve">2026-12-22</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -3791,30 +3791,30 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stavnsholtvej 41</t>
+          <t xml:space="preserve">Stiager 6</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t xml:space="preserve">3520</t>
+          <t xml:space="preserve">3500</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t xml:space="preserve">7966736</t>
+          <t xml:space="preserve">2138487</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J51">
-        <v>3594</v>
+        <v>792</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t xml:space="preserve">311216460</t>
+          <t xml:space="preserve">311219387</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -3824,7 +3824,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-12-07</t>
+          <t xml:space="preserve">2026-12-22</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -3866,30 +3866,30 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stavnsholtvej 41</t>
+          <t xml:space="preserve">Tornekrogen 64</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t xml:space="preserve">3520</t>
+          <t xml:space="preserve">3500</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t xml:space="preserve">7966736</t>
+          <t xml:space="preserve">2135624</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J52">
-        <v>6415</v>
+        <v>284</v>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t xml:space="preserve">311216459</t>
+          <t xml:space="preserve">311219369</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -3899,7 +3899,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-12-07</t>
+          <t xml:space="preserve">2026-12-22</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -3941,7 +3941,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirke Værløsevej 48C</t>
+          <t xml:space="preserve">Lejrvej 21</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t xml:space="preserve">2138121</t>
+          <t xml:space="preserve">2135260</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -3960,21 +3960,21 @@
         </is>
       </c>
       <c r="J53">
-        <v>170</v>
+        <v>445</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t xml:space="preserve">311216946</t>
+          <t xml:space="preserve">311221281</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Sweco Danmark A/S</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-12-09</t>
+          <t xml:space="preserve">2027-01-06</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -4016,7 +4016,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ballerupvej 60</t>
+          <t xml:space="preserve">Ryetvej 1</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -4026,7 +4026,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t xml:space="preserve">2138713</t>
+          <t xml:space="preserve">2136642</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -4035,11 +4035,11 @@
         </is>
       </c>
       <c r="J54">
-        <v>475</v>
+        <v>4043</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t xml:space="preserve">311218089</t>
+          <t xml:space="preserve">311221323</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -4049,7 +4049,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-12-16</t>
+          <t xml:space="preserve">2027-01-06</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirke Værløsevej 48F</t>
+          <t xml:space="preserve">Ryetvej 1</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -4101,30 +4101,30 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t xml:space="preserve">2138262</t>
+          <t xml:space="preserve">2136642</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J55">
-        <v>126</v>
+        <v>2503</v>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t xml:space="preserve">311219398</t>
+          <t xml:space="preserve">311221323</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Sweco Danmark A/S</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-12-22</t>
+          <t xml:space="preserve">2027-01-06</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -4166,40 +4166,40 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kulturtorvet 6</t>
+          <t xml:space="preserve">Ryetvej 1</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t xml:space="preserve">3520</t>
+          <t xml:space="preserve">3500</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t xml:space="preserve">2263807</t>
+          <t xml:space="preserve">2136642</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J56">
-        <v>7375</v>
+        <v>2976</v>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t xml:space="preserve">311219413</t>
+          <t xml:space="preserve">311221323</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Sweco Danmark A/S</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-12-22</t>
+          <t xml:space="preserve">2027-01-06</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skandrups Alle 7</t>
+          <t xml:space="preserve">Ryetvej 1</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -4251,20 +4251,20 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t xml:space="preserve">2134015</t>
+          <t xml:space="preserve">2136642</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J57">
-        <v>324</v>
+        <v>3139</v>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t xml:space="preserve">311219346</t>
+          <t xml:space="preserve">311221323</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -4274,7 +4274,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-12-22</t>
+          <t xml:space="preserve">2027-01-06</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -4316,7 +4316,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Solbjerghaven 4</t>
+          <t xml:space="preserve">Skovbovænget 75</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -4326,7 +4326,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t xml:space="preserve">8234925</t>
+          <t xml:space="preserve">2134177</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -4335,11 +4335,11 @@
         </is>
       </c>
       <c r="J58">
-        <v>601</v>
+        <v>487</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t xml:space="preserve">311219403</t>
+          <t xml:space="preserve">311221283</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -4349,7 +4349,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-12-22</t>
+          <t xml:space="preserve">2027-01-06</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -4391,7 +4391,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Solbjerghaven 4</t>
+          <t xml:space="preserve">Kirke Værløsevej 58</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -4401,7 +4401,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t xml:space="preserve">8234925</t>
+          <t xml:space="preserve">8736301</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -4410,11 +4410,11 @@
         </is>
       </c>
       <c r="J59">
-        <v>376</v>
+        <v>2433</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t xml:space="preserve">311219403</t>
+          <t xml:space="preserve">311222747</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -4424,7 +4424,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-12-22</t>
+          <t xml:space="preserve">2027-01-16</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -4466,7 +4466,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Solbjerghaven 4</t>
+          <t xml:space="preserve">Skovgården 1</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -4476,20 +4476,20 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t xml:space="preserve">8234925</t>
+          <t xml:space="preserve">2135631</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J60">
-        <v>376</v>
+        <v>1935</v>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t xml:space="preserve">311219403</t>
+          <t xml:space="preserve">311222743</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -4499,7 +4499,7 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-12-22</t>
+          <t xml:space="preserve">2027-01-16</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -4541,30 +4541,30 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Solbjerghaven 4</t>
+          <t xml:space="preserve">Stavnsholtvej 186</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t xml:space="preserve">3500</t>
+          <t xml:space="preserve">3520</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t xml:space="preserve">8234925</t>
+          <t xml:space="preserve">2266746</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J61">
-        <v>486</v>
+        <v>129</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t xml:space="preserve">311219403</t>
+          <t xml:space="preserve">311223980</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -4574,7 +4574,7 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-12-22</t>
+          <t xml:space="preserve">2027-01-23</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -4616,17 +4616,17 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stavnsholtvej 177</t>
+          <t xml:space="preserve">Kollekollevej 27</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t xml:space="preserve">3520</t>
+          <t xml:space="preserve">3500</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t xml:space="preserve">9046646</t>
+          <t xml:space="preserve">2138843</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -4635,11 +4635,11 @@
         </is>
       </c>
       <c r="J62">
-        <v>253</v>
+        <v>123</v>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t xml:space="preserve">311219392</t>
+          <t xml:space="preserve">311226382</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -4649,7 +4649,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-12-22</t>
+          <t xml:space="preserve">2027-02-03</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
@@ -4691,7 +4691,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stiager 6</t>
+          <t xml:space="preserve">Stiager 12</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -4701,7 +4701,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t xml:space="preserve">2138487</t>
+          <t xml:space="preserve">2138300</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -4710,11 +4710,11 @@
         </is>
       </c>
       <c r="J63">
-        <v>792</v>
+        <v>75</v>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t xml:space="preserve">311219387</t>
+          <t xml:space="preserve">311226384</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -4724,7 +4724,7 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-12-22</t>
+          <t xml:space="preserve">2027-02-03</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Storkekrogen 2</t>
+          <t xml:space="preserve">Lille Værløsevej 91</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -4776,7 +4776,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t xml:space="preserve">2134919</t>
+          <t xml:space="preserve">2138672</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -4785,11 +4785,11 @@
         </is>
       </c>
       <c r="J64">
-        <v>334</v>
+        <v>2481</v>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t xml:space="preserve">311219383</t>
+          <t xml:space="preserve">311230603</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -4799,7 +4799,7 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-12-22</t>
+          <t xml:space="preserve">2027-02-24</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -4841,7 +4841,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tornekrogen 64</t>
+          <t xml:space="preserve">Skovløbervangen 1N</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -4851,20 +4851,20 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t xml:space="preserve">2135624</t>
+          <t xml:space="preserve">2139097</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J65">
-        <v>284</v>
+        <v>1166</v>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t xml:space="preserve">311219369</t>
+          <t xml:space="preserve">311341316</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -4874,7 +4874,7 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-12-22</t>
+          <t xml:space="preserve">2027-05-19</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
@@ -4916,7 +4916,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lejrvej 21</t>
+          <t xml:space="preserve">Studekrogen 1</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -4926,7 +4926,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t xml:space="preserve">2135260</t>
+          <t xml:space="preserve">219190</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -4935,11 +4935,11 @@
         </is>
       </c>
       <c r="J66">
-        <v>445</v>
+        <v>257</v>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t xml:space="preserve">311221281</t>
+          <t xml:space="preserve">311251449</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -4949,7 +4949,7 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-01-06</t>
+          <t xml:space="preserve">2027-06-02</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
@@ -4991,7 +4991,7 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ryetvej 1</t>
+          <t xml:space="preserve">Studekrogen 1</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -5001,20 +5001,20 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t xml:space="preserve">2136642</t>
+          <t xml:space="preserve">219190</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J67">
-        <v>4043</v>
+        <v>238</v>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t xml:space="preserve">311221323</t>
+          <t xml:space="preserve">311251452</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -5024,7 +5024,7 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-01-06</t>
+          <t xml:space="preserve">2027-06-02</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
@@ -5066,7 +5066,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ryetvej 1</t>
+          <t xml:space="preserve">Studekrogen 1</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -5076,20 +5076,20 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t xml:space="preserve">2136642</t>
+          <t xml:space="preserve">219190</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J68">
-        <v>2503</v>
+        <v>368</v>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t xml:space="preserve">311221323</t>
+          <t xml:space="preserve">311251450</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -5099,7 +5099,7 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-01-06</t>
+          <t xml:space="preserve">2027-06-02</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ryetvej 1</t>
+          <t xml:space="preserve">Studekrogen 1</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -5151,20 +5151,20 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t xml:space="preserve">2136642</t>
+          <t xml:space="preserve">219190</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J69">
-        <v>2976</v>
+        <v>607</v>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t xml:space="preserve">311221323</t>
+          <t xml:space="preserve">311251452</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -5174,7 +5174,7 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-01-06</t>
+          <t xml:space="preserve">2027-06-02</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
@@ -5216,7 +5216,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ryetvej 1</t>
+          <t xml:space="preserve">Studekrogen 1</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -5226,20 +5226,20 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t xml:space="preserve">2136642</t>
+          <t xml:space="preserve">219190</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J70">
-        <v>3139</v>
+        <v>359</v>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t xml:space="preserve">311221323</t>
+          <t xml:space="preserve">311251452</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -5249,7 +5249,7 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-01-06</t>
+          <t xml:space="preserve">2027-06-02</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
@@ -5291,7 +5291,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skovbovænget 75</t>
+          <t xml:space="preserve">Studekrogen 1</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -5301,20 +5301,20 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t xml:space="preserve">2134177</t>
+          <t xml:space="preserve">219190</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J71">
-        <v>487</v>
+        <v>393</v>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t xml:space="preserve">311221283</t>
+          <t xml:space="preserve">311251452</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -5324,7 +5324,7 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-01-06</t>
+          <t xml:space="preserve">2027-06-02</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
@@ -5366,7 +5366,7 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirke Værløsevej 58</t>
+          <t xml:space="preserve">Studekrogen 1</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -5376,20 +5376,20 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t xml:space="preserve">8736301</t>
+          <t xml:space="preserve">219191</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J72">
-        <v>2433</v>
+        <v>166</v>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t xml:space="preserve">311222747</t>
+          <t xml:space="preserve">311251452</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-01-16</t>
+          <t xml:space="preserve">2027-06-02</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
@@ -5441,7 +5441,7 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skovgården 1</t>
+          <t xml:space="preserve">Poppel Alle 14</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -5451,20 +5451,20 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t xml:space="preserve">2135631</t>
+          <t xml:space="preserve">8736223</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="J73">
-        <v>1935</v>
+        <v>449</v>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t xml:space="preserve">311222743</t>
+          <t xml:space="preserve">311259430</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -5474,7 +5474,7 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-01-16</t>
+          <t xml:space="preserve">2027-07-06</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
@@ -5516,30 +5516,30 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stavnsholtvej 186</t>
+          <t xml:space="preserve">Poppel Alle 3A</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t xml:space="preserve">3520</t>
+          <t xml:space="preserve">3500</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t xml:space="preserve">2266746</t>
+          <t xml:space="preserve">8736223</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="J74">
-        <v>129</v>
+        <v>652</v>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t xml:space="preserve">311223980</t>
+          <t xml:space="preserve">311259430</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -5549,7 +5549,7 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-01-23</t>
+          <t xml:space="preserve">2027-07-06</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
@@ -5591,7 +5591,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kollekollevej 27</t>
+          <t xml:space="preserve">Poppel Alle 3C</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -5601,20 +5601,20 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t xml:space="preserve">2138843</t>
+          <t xml:space="preserve">8736223</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="J75">
-        <v>123</v>
+        <v>429</v>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t xml:space="preserve">311226382</t>
+          <t xml:space="preserve">311259430</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -5624,7 +5624,7 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-02-03</t>
+          <t xml:space="preserve">2027-07-06</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
@@ -5666,7 +5666,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stiager 12</t>
+          <t xml:space="preserve">Poppel Alle 5C</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -5676,20 +5676,20 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t xml:space="preserve">2138300</t>
+          <t xml:space="preserve">8736223</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">16</t>
         </is>
       </c>
       <c r="J76">
-        <v>75</v>
+        <v>656</v>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t xml:space="preserve">311226384</t>
+          <t xml:space="preserve">311259430</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -5699,7 +5699,7 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-02-03</t>
+          <t xml:space="preserve">2027-07-06</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
@@ -5741,7 +5741,7 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lille Værløsevej 91</t>
+          <t xml:space="preserve">Poppel Alle 6</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -5751,20 +5751,20 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t xml:space="preserve">2138672</t>
+          <t xml:space="preserve">8736223</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J77">
-        <v>2481</v>
+        <v>815</v>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t xml:space="preserve">311230603</t>
+          <t xml:space="preserve">311259430</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -5774,7 +5774,7 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-02-24</t>
+          <t xml:space="preserve">2027-07-06</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
@@ -5816,7 +5816,7 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skovløbervangen 1N</t>
+          <t xml:space="preserve">Poppel Alle 6</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -5826,20 +5826,20 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t xml:space="preserve">2139097</t>
+          <t xml:space="preserve">8736223</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J78">
-        <v>1166</v>
+        <v>213</v>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t xml:space="preserve">311341316</t>
+          <t xml:space="preserve">311259430</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -5849,7 +5849,7 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-05-19</t>
+          <t xml:space="preserve">2027-07-06</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
@@ -5891,7 +5891,7 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Studekrogen 1</t>
+          <t xml:space="preserve">Poppel Alle 6</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -5901,20 +5901,20 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t xml:space="preserve">219190</t>
+          <t xml:space="preserve">8736223</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J79">
-        <v>257</v>
+        <v>3512</v>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t xml:space="preserve">311251449</t>
+          <t xml:space="preserve">311259430</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -5924,7 +5924,7 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-06-02</t>
+          <t xml:space="preserve">2027-07-06</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
@@ -5966,7 +5966,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Studekrogen 1</t>
+          <t xml:space="preserve">Poppel Alle 6</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -5976,20 +5976,20 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t xml:space="preserve">219190</t>
+          <t xml:space="preserve">8736223</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J80">
-        <v>238</v>
+        <v>1679</v>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t xml:space="preserve">311251452</t>
+          <t xml:space="preserve">311259430</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -5999,7 +5999,7 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-06-02</t>
+          <t xml:space="preserve">2027-07-06</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
@@ -6041,7 +6041,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Studekrogen 1</t>
+          <t xml:space="preserve">Poppel Alle 9</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -6051,20 +6051,20 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t xml:space="preserve">219190</t>
+          <t xml:space="preserve">8736223</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">22</t>
         </is>
       </c>
       <c r="J81">
-        <v>368</v>
+        <v>339</v>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t xml:space="preserve">311251450</t>
+          <t xml:space="preserve">311259430</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -6074,7 +6074,7 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-06-02</t>
+          <t xml:space="preserve">2027-07-06</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
@@ -6116,7 +6116,7 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Studekrogen 1</t>
+          <t xml:space="preserve">Stiager 2</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -6126,30 +6126,30 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t xml:space="preserve">219190</t>
+          <t xml:space="preserve">2138477</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J82">
-        <v>607</v>
+        <v>6523</v>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t xml:space="preserve">311251452</t>
+          <t xml:space="preserve">311262025</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sweco Danmark A/S</t>
+          <t xml:space="preserve">Topdahl ApS</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-06-02</t>
+          <t xml:space="preserve">2027-07-21</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
@@ -6191,30 +6191,30 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Studekrogen 1</t>
+          <t xml:space="preserve">Hvilebækgårdsvej 1</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t xml:space="preserve">3500</t>
+          <t xml:space="preserve">3520</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t xml:space="preserve">219190</t>
+          <t xml:space="preserve">2266459</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J83">
-        <v>359</v>
+        <v>1058</v>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t xml:space="preserve">311251452</t>
+          <t xml:space="preserve">311280823</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -6224,7 +6224,7 @@
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-06-02</t>
+          <t xml:space="preserve">2027-10-27</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
@@ -6266,30 +6266,30 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Studekrogen 1</t>
+          <t xml:space="preserve">Hvilebækgårdsvej 1</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t xml:space="preserve">3500</t>
+          <t xml:space="preserve">3520</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t xml:space="preserve">219190</t>
+          <t xml:space="preserve">2266459</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J84">
-        <v>393</v>
+        <v>1263</v>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t xml:space="preserve">311251452</t>
+          <t xml:space="preserve">311280823</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
@@ -6299,7 +6299,7 @@
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-06-02</t>
+          <t xml:space="preserve">2027-10-27</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
@@ -6341,30 +6341,30 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t xml:space="preserve">Studekrogen 1</t>
+          <t xml:space="preserve">Hvilebækgårdsvej 1</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t xml:space="preserve">3500</t>
+          <t xml:space="preserve">3520</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t xml:space="preserve">219191</t>
+          <t xml:space="preserve">2266459</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J85">
-        <v>166</v>
+        <v>1075</v>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t xml:space="preserve">311251452</t>
+          <t xml:space="preserve">311280823</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -6374,7 +6374,7 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-06-02</t>
+          <t xml:space="preserve">2027-10-27</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
@@ -6416,30 +6416,30 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t xml:space="preserve">Poppel Alle 14</t>
+          <t xml:space="preserve">Hvilebækgårdsvej 1</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t xml:space="preserve">3500</t>
+          <t xml:space="preserve">3520</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t xml:space="preserve">8736223</t>
+          <t xml:space="preserve">2266459</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J86">
-        <v>449</v>
+        <v>317</v>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t xml:space="preserve">311259430</t>
+          <t xml:space="preserve">311280823</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -6449,7 +6449,7 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-06</t>
+          <t xml:space="preserve">2027-10-27</t>
         </is>
       </c>
       <c r="N86" t="inlineStr">
@@ -6491,30 +6491,30 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t xml:space="preserve">Poppel Alle 3A</t>
+          <t xml:space="preserve">Hvilebækgårdsvej 1</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t xml:space="preserve">3500</t>
+          <t xml:space="preserve">3520</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t xml:space="preserve">8736223</t>
+          <t xml:space="preserve">2266459</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J87">
-        <v>652</v>
+        <v>1049</v>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t xml:space="preserve">311259430</t>
+          <t xml:space="preserve">311280823</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
@@ -6524,7 +6524,7 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-06</t>
+          <t xml:space="preserve">2027-10-27</t>
         </is>
       </c>
       <c r="N87" t="inlineStr">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t xml:space="preserve">Poppel Alle 3C</t>
+          <t xml:space="preserve">Birkevang 17</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -6576,20 +6576,20 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t xml:space="preserve">8736223</t>
+          <t xml:space="preserve">2134114</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J88">
-        <v>429</v>
+        <v>505</v>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t xml:space="preserve">311259430</t>
+          <t xml:space="preserve">311344564</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -6599,7 +6599,7 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-06</t>
+          <t xml:space="preserve">2028-11-01</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">
@@ -6641,7 +6641,7 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t xml:space="preserve">Poppel Alle 5C</t>
+          <t xml:space="preserve">Dalsø Park 107</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -6651,20 +6651,20 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t xml:space="preserve">8736223</t>
+          <t xml:space="preserve">2135069</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t xml:space="preserve">16</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J89">
-        <v>656</v>
+        <v>378</v>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t xml:space="preserve">311259430</t>
+          <t xml:space="preserve">311344550</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
@@ -6674,7 +6674,7 @@
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-06</t>
+          <t xml:space="preserve">2028-11-01</t>
         </is>
       </c>
       <c r="N89" t="inlineStr">
@@ -6716,7 +6716,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t xml:space="preserve">Poppel Alle 6</t>
+          <t xml:space="preserve">Dalsø Park 109</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -6726,20 +6726,20 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t xml:space="preserve">8736223</t>
+          <t xml:space="preserve">2135070</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J90">
-        <v>815</v>
+        <v>482</v>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t xml:space="preserve">311259430</t>
+          <t xml:space="preserve">311344551</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
@@ -6749,7 +6749,7 @@
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-06</t>
+          <t xml:space="preserve">2028-11-01</t>
         </is>
       </c>
       <c r="N90" t="inlineStr">
@@ -6791,7 +6791,7 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t xml:space="preserve">Poppel Alle 6</t>
+          <t xml:space="preserve">Jonstrupvangvej 159</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -6801,20 +6801,20 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t xml:space="preserve">8736223</t>
+          <t xml:space="preserve">7589453</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J91">
-        <v>213</v>
+        <v>396</v>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t xml:space="preserve">311259430</t>
+          <t xml:space="preserve">311344560</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
@@ -6824,7 +6824,7 @@
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-06</t>
+          <t xml:space="preserve">2028-11-01</t>
         </is>
       </c>
       <c r="N91" t="inlineStr">
@@ -6866,7 +6866,7 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t xml:space="preserve">Poppel Alle 6</t>
+          <t xml:space="preserve">Birkevang 14A</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -6876,20 +6876,20 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t xml:space="preserve">8736223</t>
+          <t xml:space="preserve">2134241</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J92">
-        <v>3512</v>
+        <v>497</v>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t xml:space="preserve">311259430</t>
+          <t xml:space="preserve">311344821</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -6899,7 +6899,7 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-06</t>
+          <t xml:space="preserve">2028-11-02</t>
         </is>
       </c>
       <c r="N92" t="inlineStr">
@@ -6941,7 +6941,7 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t xml:space="preserve">Poppel Alle 6</t>
+          <t xml:space="preserve">Birkevang 14A</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -6951,20 +6951,20 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t xml:space="preserve">8736223</t>
+          <t xml:space="preserve">2134241</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J93">
-        <v>1679</v>
+        <v>92</v>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t xml:space="preserve">311259430</t>
+          <t xml:space="preserve">311344821</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -6974,7 +6974,7 @@
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-06</t>
+          <t xml:space="preserve">2028-11-02</t>
         </is>
       </c>
       <c r="N93" t="inlineStr">
@@ -7016,7 +7016,7 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t xml:space="preserve">Poppel Alle 9</t>
+          <t xml:space="preserve">Bymidten 46</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -7026,20 +7026,20 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t xml:space="preserve">8736223</t>
+          <t xml:space="preserve">9771981</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t xml:space="preserve">22</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J94">
-        <v>339</v>
+        <v>784</v>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t xml:space="preserve">311259430</t>
+          <t xml:space="preserve">311347476</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
@@ -7049,7 +7049,7 @@
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-06</t>
+          <t xml:space="preserve">2028-11-19</t>
         </is>
       </c>
       <c r="N94" t="inlineStr">
@@ -7091,7 +7091,7 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stiager 2</t>
+          <t xml:space="preserve">Bymidten 44</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -7101,7 +7101,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t xml:space="preserve">2138477</t>
+          <t xml:space="preserve">2136043</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -7110,21 +7110,21 @@
         </is>
       </c>
       <c r="J95">
-        <v>6523</v>
+        <v>739</v>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t xml:space="preserve">311262025</t>
+          <t xml:space="preserve">311348330</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t xml:space="preserve">Topdahl ApS</t>
+          <t xml:space="preserve">Sweco Danmark A/S</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-21</t>
+          <t xml:space="preserve">2028-11-23</t>
         </is>
       </c>
       <c r="N95" t="inlineStr">
@@ -7166,17 +7166,17 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hvilebækgårdsvej 1</t>
+          <t xml:space="preserve">Smedegade 5A</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t xml:space="preserve">3520</t>
+          <t xml:space="preserve">3500</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t xml:space="preserve">2266459</t>
+          <t xml:space="preserve">2134736</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -7185,21 +7185,21 @@
         </is>
       </c>
       <c r="J96">
-        <v>1058</v>
+        <v>210</v>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t xml:space="preserve">311280823</t>
+          <t xml:space="preserve">311349213</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sweco Danmark A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-10-27</t>
+          <t xml:space="preserve">2028-11-29</t>
         </is>
       </c>
       <c r="N96" t="inlineStr">
@@ -7241,17 +7241,17 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hvilebækgårdsvej 1</t>
+          <t xml:space="preserve">Smedegade 5B</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t xml:space="preserve">3520</t>
+          <t xml:space="preserve">3500</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t xml:space="preserve">2266459</t>
+          <t xml:space="preserve">2134736</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -7260,21 +7260,21 @@
         </is>
       </c>
       <c r="J97">
-        <v>1263</v>
+        <v>104</v>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t xml:space="preserve">311280823</t>
+          <t xml:space="preserve">311349213</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sweco Danmark A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-10-27</t>
+          <t xml:space="preserve">2028-11-29</t>
         </is>
       </c>
       <c r="N97" t="inlineStr">
@@ -7316,30 +7316,30 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hvilebækgårdsvej 1</t>
+          <t xml:space="preserve">Lerstedet 1A</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t xml:space="preserve">3520</t>
+          <t xml:space="preserve">3500</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t xml:space="preserve">2266459</t>
+          <t xml:space="preserve">2137228</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J98">
-        <v>1075</v>
+        <v>250</v>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t xml:space="preserve">311280823</t>
+          <t xml:space="preserve">311351114</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
@@ -7349,7 +7349,7 @@
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-10-27</t>
+          <t xml:space="preserve">2028-12-12</t>
         </is>
       </c>
       <c r="N98" t="inlineStr">
@@ -7391,30 +7391,30 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hvilebækgårdsvej 1</t>
+          <t xml:space="preserve">Skovløbervangen 1</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t xml:space="preserve">3520</t>
+          <t xml:space="preserve">3500</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t xml:space="preserve">2266459</t>
+          <t xml:space="preserve">2139097</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J99">
-        <v>317</v>
+        <v>6137</v>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t xml:space="preserve">311280823</t>
+          <t xml:space="preserve">311356615</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
@@ -7424,7 +7424,7 @@
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-10-27</t>
+          <t xml:space="preserve">2029-01-25</t>
         </is>
       </c>
       <c r="N99" t="inlineStr">
@@ -7466,30 +7466,30 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hvilebækgårdsvej 1</t>
+          <t xml:space="preserve">Skovløbervangen 1</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t xml:space="preserve">3520</t>
+          <t xml:space="preserve">3500</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t xml:space="preserve">2266459</t>
+          <t xml:space="preserve">2139097</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J100">
-        <v>1049</v>
+        <v>2838</v>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t xml:space="preserve">311280823</t>
+          <t xml:space="preserve">311356615</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
@@ -7499,7 +7499,7 @@
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-10-27</t>
+          <t xml:space="preserve">2029-01-25</t>
         </is>
       </c>
       <c r="N100" t="inlineStr">
@@ -7541,7 +7541,7 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t xml:space="preserve">Birkevang 17</t>
+          <t xml:space="preserve">Bymidten 48</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -7551,20 +7551,20 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t xml:space="preserve">2134114</t>
+          <t xml:space="preserve">9771981</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J101">
-        <v>505</v>
+        <v>4779</v>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t xml:space="preserve">311344564</t>
+          <t xml:space="preserve">311357180</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
@@ -7574,7 +7574,7 @@
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-11-01</t>
+          <t xml:space="preserve">2029-01-30</t>
         </is>
       </c>
       <c r="N101" t="inlineStr">
@@ -7616,7 +7616,7 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dalsø Park 107</t>
+          <t xml:space="preserve">Månedalstien 6</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -7626,7 +7626,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t xml:space="preserve">2135069</t>
+          <t xml:space="preserve">2134113</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -7635,11 +7635,11 @@
         </is>
       </c>
       <c r="J102">
-        <v>378</v>
+        <v>290</v>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t xml:space="preserve">311344550</t>
+          <t xml:space="preserve">311357179</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
@@ -7649,7 +7649,7 @@
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-11-01</t>
+          <t xml:space="preserve">2029-01-30</t>
         </is>
       </c>
       <c r="N102" t="inlineStr">
@@ -7691,7 +7691,7 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dalsø Park 109</t>
+          <t xml:space="preserve">Poppel Alle 13</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -7701,7 +7701,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t xml:space="preserve">2135070</t>
+          <t xml:space="preserve">2133873</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -7710,11 +7710,11 @@
         </is>
       </c>
       <c r="J103">
-        <v>482</v>
+        <v>711</v>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t xml:space="preserve">311344551</t>
+          <t xml:space="preserve">311359733</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
@@ -7724,7 +7724,7 @@
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-11-01</t>
+          <t xml:space="preserve">2029-02-15</t>
         </is>
       </c>
       <c r="N103" t="inlineStr">
@@ -7766,7 +7766,7 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jonstrupvangvej 159</t>
+          <t xml:space="preserve">Kirke Værløsevej 50</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -7776,7 +7776,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t xml:space="preserve">7589453</t>
+          <t xml:space="preserve">2138262</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -7785,11 +7785,11 @@
         </is>
       </c>
       <c r="J104">
-        <v>396</v>
+        <v>1977</v>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t xml:space="preserve">311344560</t>
+          <t xml:space="preserve">311360757</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
@@ -7799,7 +7799,7 @@
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-11-01</t>
+          <t xml:space="preserve">2029-02-21</t>
         </is>
       </c>
       <c r="N104" t="inlineStr">
@@ -7841,7 +7841,7 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t xml:space="preserve">Birkevang 14A</t>
+          <t xml:space="preserve">Kirke Værløsevej 50</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -7851,20 +7851,20 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t xml:space="preserve">2134241</t>
+          <t xml:space="preserve">2138262</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J105">
-        <v>497</v>
+        <v>1435</v>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t xml:space="preserve">311344821</t>
+          <t xml:space="preserve">311360757</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-11-02</t>
+          <t xml:space="preserve">2029-02-21</t>
         </is>
       </c>
       <c r="N105" t="inlineStr">
@@ -7916,7 +7916,7 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t xml:space="preserve">Birkevang 14A</t>
+          <t xml:space="preserve">Kirke Værløsevej 50</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -7926,7 +7926,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t xml:space="preserve">2134241</t>
+          <t xml:space="preserve">2138262</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -7935,11 +7935,11 @@
         </is>
       </c>
       <c r="J106">
-        <v>92</v>
+        <v>8023</v>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t xml:space="preserve">311344821</t>
+          <t xml:space="preserve">311360757</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
@@ -7949,7 +7949,7 @@
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-11-02</t>
+          <t xml:space="preserve">2029-02-21</t>
         </is>
       </c>
       <c r="N106" t="inlineStr">
@@ -7991,7 +7991,7 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bymidten 46</t>
+          <t xml:space="preserve">Kirke Værløsevej 50</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -8001,20 +8001,20 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t xml:space="preserve">9771981</t>
+          <t xml:space="preserve">2138262</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J107">
-        <v>784</v>
+        <v>812</v>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t xml:space="preserve">311347476</t>
+          <t xml:space="preserve">311360757</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
@@ -8024,7 +8024,7 @@
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-11-19</t>
+          <t xml:space="preserve">2029-02-21</t>
         </is>
       </c>
       <c r="N107" t="inlineStr">
@@ -8066,7 +8066,7 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bymidten 44</t>
+          <t xml:space="preserve">Ballerupvej 29A</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -8076,20 +8076,20 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t xml:space="preserve">2136043</t>
+          <t xml:space="preserve">2138944</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J108">
-        <v>739</v>
+        <v>158</v>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t xml:space="preserve">311348330</t>
+          <t xml:space="preserve">311367951</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
@@ -8099,7 +8099,7 @@
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-11-23</t>
+          <t xml:space="preserve">2029-03-29</t>
         </is>
       </c>
       <c r="N108" t="inlineStr">
@@ -8141,7 +8141,7 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t xml:space="preserve">Smedegade 5A</t>
+          <t xml:space="preserve">Ballerupvej 31</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
@@ -8151,7 +8151,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t xml:space="preserve">2134736</t>
+          <t xml:space="preserve">2138944</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -8160,21 +8160,21 @@
         </is>
       </c>
       <c r="J109">
-        <v>210</v>
+        <v>186</v>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t xml:space="preserve">311349213</t>
+          <t xml:space="preserve">311367953</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Sweco Danmark A/S</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-11-29</t>
+          <t xml:space="preserve">2029-03-29</t>
         </is>
       </c>
       <c r="N109" t="inlineStr">
@@ -8216,7 +8216,7 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t xml:space="preserve">Smedegade 5B</t>
+          <t xml:space="preserve">Højeloft Vænge 4</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
@@ -8226,30 +8226,30 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t xml:space="preserve">2134736</t>
+          <t xml:space="preserve">2138099</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J110">
-        <v>104</v>
+        <v>1053</v>
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t xml:space="preserve">311349213</t>
+          <t xml:space="preserve">311367947</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Sweco Danmark A/S</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-11-29</t>
+          <t xml:space="preserve">2029-03-29</t>
         </is>
       </c>
       <c r="N110" t="inlineStr">
@@ -8291,7 +8291,7 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lerstedet 1A</t>
+          <t xml:space="preserve">Jonstrupvangvej 150A</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
@@ -8301,20 +8301,20 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t xml:space="preserve">2137228</t>
+          <t xml:space="preserve">7869009</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J111">
-        <v>250</v>
+        <v>2459</v>
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t xml:space="preserve">311351114</t>
+          <t xml:space="preserve">311367955</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
@@ -8324,7 +8324,7 @@
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-12-12</t>
+          <t xml:space="preserve">2029-03-29</t>
         </is>
       </c>
       <c r="N111" t="inlineStr">
@@ -8366,7 +8366,7 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skovløbervangen 1</t>
+          <t xml:space="preserve">Jonstrupvangvej 150E</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
@@ -8376,20 +8376,20 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t xml:space="preserve">2139097</t>
+          <t xml:space="preserve">7869009</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J112">
-        <v>6137</v>
+        <v>361</v>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t xml:space="preserve">311356615</t>
+          <t xml:space="preserve">311367955</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
@@ -8399,7 +8399,7 @@
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-01-25</t>
+          <t xml:space="preserve">2029-03-29</t>
         </is>
       </c>
       <c r="N112" t="inlineStr">
@@ -8441,7 +8441,7 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skovløbervangen 1</t>
+          <t xml:space="preserve">Jonstrupvangvej 150H</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
@@ -8451,20 +8451,20 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t xml:space="preserve">2139097</t>
+          <t xml:space="preserve">7869009</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J113">
-        <v>2838</v>
+        <v>931</v>
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t xml:space="preserve">311356615</t>
+          <t xml:space="preserve">311367955</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
@@ -8474,7 +8474,7 @@
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-01-25</t>
+          <t xml:space="preserve">2029-03-29</t>
         </is>
       </c>
       <c r="N113" t="inlineStr">
@@ -8516,7 +8516,7 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bymidten 48</t>
+          <t xml:space="preserve">Jonstrupvangvej 150M</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
@@ -8526,20 +8526,20 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t xml:space="preserve">9771981</t>
+          <t xml:space="preserve">7869009</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J114">
-        <v>4779</v>
+        <v>604</v>
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t xml:space="preserve">311357180</t>
+          <t xml:space="preserve">311367955</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
@@ -8549,7 +8549,7 @@
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-01-30</t>
+          <t xml:space="preserve">2029-03-29</t>
         </is>
       </c>
       <c r="N114" t="inlineStr">
@@ -8591,7 +8591,7 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t xml:space="preserve">Månedalstien 6</t>
+          <t xml:space="preserve">Lille Værløsevej 36A</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
@@ -8601,7 +8601,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t xml:space="preserve">2134113</t>
+          <t xml:space="preserve">2136270</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -8610,11 +8610,11 @@
         </is>
       </c>
       <c r="J115">
-        <v>290</v>
+        <v>152</v>
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t xml:space="preserve">311357179</t>
+          <t xml:space="preserve">311367948</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
@@ -8624,7 +8624,7 @@
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-01-30</t>
+          <t xml:space="preserve">2029-03-29</t>
         </is>
       </c>
       <c r="N115" t="inlineStr">
@@ -8666,7 +8666,7 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Poppel Alle 13</t>
+          <t xml:space="preserve">Poppel Alle 19A</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
@@ -8676,7 +8676,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t xml:space="preserve">2133873</t>
+          <t xml:space="preserve">2133870</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -8685,11 +8685,11 @@
         </is>
       </c>
       <c r="J116">
-        <v>711</v>
+        <v>175</v>
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t xml:space="preserve">311359733</t>
+          <t xml:space="preserve">311367949</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
@@ -8699,7 +8699,7 @@
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-02-15</t>
+          <t xml:space="preserve">2029-03-29</t>
         </is>
       </c>
       <c r="N116" t="inlineStr">
@@ -8741,7 +8741,7 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirke Værløsevej 50</t>
+          <t xml:space="preserve">Poppel Alle 19B</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
@@ -8751,20 +8751,20 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t xml:space="preserve">2138262</t>
+          <t xml:space="preserve">2133870</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J117">
-        <v>1977</v>
+        <v>213</v>
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t xml:space="preserve">311360757</t>
+          <t xml:space="preserve">311367949</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
@@ -8774,7 +8774,7 @@
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-02-21</t>
+          <t xml:space="preserve">2029-03-29</t>
         </is>
       </c>
       <c r="N117" t="inlineStr">
@@ -8816,7 +8816,7 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirke Værløsevej 50</t>
+          <t xml:space="preserve">Poppel Alle 19C</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
@@ -8826,20 +8826,20 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t xml:space="preserve">2138262</t>
+          <t xml:space="preserve">2133870</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J118">
-        <v>1435</v>
+        <v>119</v>
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t xml:space="preserve">311360757</t>
+          <t xml:space="preserve">311367949</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
@@ -8849,7 +8849,7 @@
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-02-21</t>
+          <t xml:space="preserve">2029-03-29</t>
         </is>
       </c>
       <c r="N118" t="inlineStr">
@@ -8891,7 +8891,7 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirke Værløsevej 50</t>
+          <t xml:space="preserve">Poppel Alle 19D</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
@@ -8901,7 +8901,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t xml:space="preserve">2138262</t>
+          <t xml:space="preserve">2133870</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -8910,11 +8910,11 @@
         </is>
       </c>
       <c r="J119">
-        <v>8023</v>
+        <v>189</v>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t xml:space="preserve">311360757</t>
+          <t xml:space="preserve">311367949</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
@@ -8924,7 +8924,7 @@
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-02-21</t>
+          <t xml:space="preserve">2029-03-29</t>
         </is>
       </c>
       <c r="N119" t="inlineStr">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirke Værløsevej 50</t>
+          <t xml:space="preserve">Højeloft Vænge 2A</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
@@ -8976,20 +8976,20 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t xml:space="preserve">2138262</t>
+          <t xml:space="preserve">2138099</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J120">
-        <v>812</v>
+        <v>207</v>
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t xml:space="preserve">311360757</t>
+          <t xml:space="preserve">311373723</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
@@ -8999,7 +8999,7 @@
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-02-21</t>
+          <t xml:space="preserve">2029-04-30</t>
         </is>
       </c>
       <c r="N120" t="inlineStr">
@@ -9041,7 +9041,7 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ballerupvej 29A</t>
+          <t xml:space="preserve">Skovgårds Alle 37</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
@@ -9051,20 +9051,20 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t xml:space="preserve">2138944</t>
+          <t xml:space="preserve">8736300</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J121">
-        <v>158</v>
+        <v>130</v>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t xml:space="preserve">311367951</t>
+          <t xml:space="preserve">311374640</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
@@ -9074,7 +9074,7 @@
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-03-29</t>
+          <t xml:space="preserve">2029-05-03</t>
         </is>
       </c>
       <c r="N121" t="inlineStr">
@@ -9116,7 +9116,7 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ballerupvej 31</t>
+          <t xml:space="preserve">Skovgårds Alle 37</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
@@ -9126,20 +9126,20 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t xml:space="preserve">2138944</t>
+          <t xml:space="preserve">8736300</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J122">
-        <v>186</v>
+        <v>399</v>
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t xml:space="preserve">311367953</t>
+          <t xml:space="preserve">311374640</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
@@ -9149,7 +9149,7 @@
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-03-29</t>
+          <t xml:space="preserve">2029-05-03</t>
         </is>
       </c>
       <c r="N122" t="inlineStr">
@@ -9191,7 +9191,7 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Højeloft Vænge 4</t>
+          <t xml:space="preserve">Skovgårds Alle 37</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
@@ -9201,7 +9201,7 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t xml:space="preserve">2138099</t>
+          <t xml:space="preserve">8736300</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -9210,11 +9210,11 @@
         </is>
       </c>
       <c r="J123">
-        <v>1053</v>
+        <v>113</v>
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t xml:space="preserve">311367947</t>
+          <t xml:space="preserve">311374640</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-03-29</t>
+          <t xml:space="preserve">2029-05-03</t>
         </is>
       </c>
       <c r="N123" t="inlineStr">
@@ -9266,7 +9266,7 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jonstrupvangvej 150A</t>
+          <t xml:space="preserve">Skovmose Alle 55</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
@@ -9276,7 +9276,7 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t xml:space="preserve">7869009</t>
+          <t xml:space="preserve">2133582</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -9285,21 +9285,21 @@
         </is>
       </c>
       <c r="J124">
-        <v>2459</v>
+        <v>918</v>
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t xml:space="preserve">311367955</t>
+          <t xml:space="preserve">311403713</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sweco Danmark A/S</t>
+          <t xml:space="preserve">LM Energiconsult</t>
         </is>
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-03-29</t>
+          <t xml:space="preserve">2029-10-14</t>
         </is>
       </c>
       <c r="N124" t="inlineStr">
@@ -9341,7 +9341,7 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jonstrupvangvej 150E</t>
+          <t xml:space="preserve">Syvstjerne Vænge 10A</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
@@ -9351,30 +9351,30 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t xml:space="preserve">7869009</t>
+          <t xml:space="preserve">2137661</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J125">
-        <v>361</v>
+        <v>440</v>
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t xml:space="preserve">311367955</t>
+          <t xml:space="preserve">311481142</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sweco Danmark A/S</t>
+          <t xml:space="preserve">Trykprøvning &amp; Energimærkning Danmark ApS</t>
         </is>
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-03-29</t>
+          <t xml:space="preserve">2030-12-07</t>
         </is>
       </c>
       <c r="N125" t="inlineStr">
@@ -9416,7 +9416,7 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jonstrupvangvej 150H</t>
+          <t xml:space="preserve">Kirke Værløsevej 48D</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
@@ -9426,30 +9426,30 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t xml:space="preserve">7869009</t>
+          <t xml:space="preserve">2138127</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J126">
-        <v>931</v>
+        <v>954</v>
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t xml:space="preserve">311367955</t>
+          <t xml:space="preserve">311544743</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sweco Danmark A/S</t>
+          <t xml:space="preserve">Trykprøvning &amp; Energimærkning Danmark ApS</t>
         </is>
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-03-29</t>
+          <t xml:space="preserve">2031-08-31</t>
         </is>
       </c>
       <c r="N126" t="inlineStr">
@@ -9491,7 +9491,7 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jonstrupvangvej 150M</t>
+          <t xml:space="preserve">Ballerupvej 29</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
@@ -9501,30 +9501,30 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t xml:space="preserve">7869009</t>
+          <t xml:space="preserve">217538, 217539</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J127">
-        <v>604</v>
+        <v>704</v>
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t xml:space="preserve">311367955</t>
+          <t xml:space="preserve">311596730</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sweco Danmark A/S</t>
+          <t xml:space="preserve">Domutech A/S</t>
         </is>
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-03-29</t>
+          <t xml:space="preserve">2032-04-29</t>
         </is>
       </c>
       <c r="N127" t="inlineStr">
@@ -9566,7 +9566,7 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lille Værløsevej 36A</t>
+          <t xml:space="preserve">Skovgården 2A</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
@@ -9576,7 +9576,7 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t xml:space="preserve">2136270</t>
+          <t xml:space="preserve">217474, 217475</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -9585,21 +9585,21 @@
         </is>
       </c>
       <c r="J128">
-        <v>152</v>
+        <v>316</v>
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t xml:space="preserve">311367948</t>
+          <t xml:space="preserve">311621249</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sweco Danmark A/S</t>
+          <t xml:space="preserve">Domutech A/S</t>
         </is>
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-03-29</t>
+          <t xml:space="preserve">2032-08-18</t>
         </is>
       </c>
       <c r="N128" t="inlineStr">
@@ -9641,17 +9641,17 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t xml:space="preserve">Poppel Alle 19A</t>
+          <t xml:space="preserve">Lillevænget 1A</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t xml:space="preserve">3500</t>
+          <t xml:space="preserve">3520</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t xml:space="preserve">2133870</t>
+          <t xml:space="preserve">244717</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -9660,21 +9660,21 @@
         </is>
       </c>
       <c r="J129">
-        <v>175</v>
+        <v>1352</v>
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t xml:space="preserve">311367949</t>
+          <t xml:space="preserve">311626228</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sweco Danmark A/S</t>
+          <t xml:space="preserve">Domutech A/S</t>
         </is>
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-03-29</t>
+          <t xml:space="preserve">2032-09-07</t>
         </is>
       </c>
       <c r="N129" t="inlineStr">
@@ -9716,40 +9716,40 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t xml:space="preserve">Poppel Alle 19B</t>
+          <t xml:space="preserve">Ryttergårdsvej 100</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t xml:space="preserve">3500</t>
+          <t xml:space="preserve">3520</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t xml:space="preserve">2133870</t>
+          <t xml:space="preserve">2263883</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J130">
-        <v>213</v>
+        <v>717</v>
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t xml:space="preserve">311367949</t>
+          <t xml:space="preserve">311631857</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sweco Danmark A/S</t>
+          <t xml:space="preserve">Dinraadgivning ApS</t>
         </is>
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-03-29</t>
+          <t xml:space="preserve">2032-09-28</t>
         </is>
       </c>
       <c r="N130" t="inlineStr">
@@ -9791,7 +9791,7 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t xml:space="preserve">Poppel Alle 19C</t>
+          <t xml:space="preserve">Helikoptervej 7</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
@@ -9801,30 +9801,30 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t xml:space="preserve">2133870</t>
+          <t xml:space="preserve">100352101</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">413</t>
         </is>
       </c>
       <c r="J131">
-        <v>119</v>
+        <v>467</v>
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t xml:space="preserve">311367949</t>
+          <t xml:space="preserve">311642385</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sweco Danmark A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-03-29</t>
+          <t xml:space="preserve">2032-11-14</t>
         </is>
       </c>
       <c r="N131" t="inlineStr">
@@ -9866,40 +9866,40 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t xml:space="preserve">Poppel Alle 19D</t>
+          <t xml:space="preserve">Farum Hovedgade 84</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t xml:space="preserve">3500</t>
+          <t xml:space="preserve">3520</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t xml:space="preserve">2133870</t>
+          <t xml:space="preserve">2262452</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J132">
-        <v>189</v>
+        <v>475</v>
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t xml:space="preserve">311367949</t>
+          <t xml:space="preserve">311645153</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sweco Danmark A/S</t>
+          <t xml:space="preserve">LKH Rådgivning</t>
         </is>
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-03-29</t>
+          <t xml:space="preserve">2032-11-25</t>
         </is>
       </c>
       <c r="N132" t="inlineStr">
@@ -9941,17 +9941,17 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t xml:space="preserve">Højeloft Vænge 2A</t>
+          <t xml:space="preserve">Gammelgårdsvej 15</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t xml:space="preserve">3500</t>
+          <t xml:space="preserve">3520</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t xml:space="preserve">2138099</t>
+          <t xml:space="preserve">2263023</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -9960,21 +9960,21 @@
         </is>
       </c>
       <c r="J133">
-        <v>207</v>
+        <v>288</v>
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t xml:space="preserve">311373723</t>
+          <t xml:space="preserve">311645147</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sweco Danmark A/S</t>
+          <t xml:space="preserve">LKH Rådgivning</t>
         </is>
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-04-30</t>
+          <t xml:space="preserve">2032-11-25</t>
         </is>
       </c>
       <c r="N133" t="inlineStr">
@@ -10016,40 +10016,40 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skovgårds Alle 37</t>
+          <t xml:space="preserve">Hvilebækgårdsvej 19</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t xml:space="preserve">3500</t>
+          <t xml:space="preserve">3520</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t xml:space="preserve">8736300</t>
+          <t xml:space="preserve">2266425</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J134">
-        <v>130</v>
+        <v>531</v>
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t xml:space="preserve">311374640</t>
+          <t xml:space="preserve">311645148</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sweco Danmark A/S</t>
+          <t xml:space="preserve">LKH Rådgivning</t>
         </is>
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-05-03</t>
+          <t xml:space="preserve">2032-11-25</t>
         </is>
       </c>
       <c r="N134" t="inlineStr">
@@ -10091,40 +10091,40 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skovgårds Alle 37</t>
+          <t xml:space="preserve">Lindegårdsvej 2</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t xml:space="preserve">3500</t>
+          <t xml:space="preserve">3520</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t xml:space="preserve">8736300</t>
+          <t xml:space="preserve">2262178</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J135">
-        <v>399</v>
+        <v>241</v>
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t xml:space="preserve">311374640</t>
+          <t xml:space="preserve">311645154</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sweco Danmark A/S</t>
+          <t xml:space="preserve">LKH Rådgivning</t>
         </is>
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-05-03</t>
+          <t xml:space="preserve">2032-11-25</t>
         </is>
       </c>
       <c r="N135" t="inlineStr">
@@ -10166,40 +10166,40 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skovgårds Alle 37</t>
+          <t xml:space="preserve">Hvilebækgårdsvej 15</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t xml:space="preserve">3500</t>
+          <t xml:space="preserve">3520</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t xml:space="preserve">8736300</t>
+          <t xml:space="preserve">2266425</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J136">
-        <v>113</v>
+        <v>439</v>
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t xml:space="preserve">311374640</t>
+          <t xml:space="preserve">311645492</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sweco Danmark A/S</t>
+          <t xml:space="preserve">LKH Rådgivning</t>
         </is>
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-05-03</t>
+          <t xml:space="preserve">2032-11-28</t>
         </is>
       </c>
       <c r="N136" t="inlineStr">
@@ -10241,40 +10241,40 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skovmose Alle 55</t>
+          <t xml:space="preserve">Hvilebækgårdsvej 17</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t xml:space="preserve">3500</t>
+          <t xml:space="preserve">3520</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t xml:space="preserve">2133582</t>
+          <t xml:space="preserve">2266425</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J137">
-        <v>918</v>
+        <v>372</v>
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t xml:space="preserve">311403713</t>
+          <t xml:space="preserve">311645492</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t xml:space="preserve">LM Energiconsult</t>
+          <t xml:space="preserve">LKH Rådgivning</t>
         </is>
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-10-14</t>
+          <t xml:space="preserve">2032-11-28</t>
         </is>
       </c>
       <c r="N137" t="inlineStr">
@@ -10316,40 +10316,40 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t xml:space="preserve">Syvstjerne Vænge 10A</t>
+          <t xml:space="preserve">Nordtoftevej 56B</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t xml:space="preserve">3500</t>
+          <t xml:space="preserve">3520</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t xml:space="preserve">2137661</t>
+          <t xml:space="preserve">2262618</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J138">
-        <v>440</v>
+        <v>632</v>
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t xml:space="preserve">311481142</t>
+          <t xml:space="preserve">311645490</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t xml:space="preserve">Trykprøvning &amp; Energimærkning Danmark ApS</t>
+          <t xml:space="preserve">LKH Rådgivning</t>
         </is>
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-12-07</t>
+          <t xml:space="preserve">2032-11-28</t>
         </is>
       </c>
       <c r="N138" t="inlineStr">
@@ -10391,17 +10391,17 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirke Værløsevej 48D</t>
+          <t xml:space="preserve">Stavnsholtvej 171</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t xml:space="preserve">3500</t>
+          <t xml:space="preserve">3520</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t xml:space="preserve">2138127</t>
+          <t xml:space="preserve">8483113</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -10410,21 +10410,21 @@
         </is>
       </c>
       <c r="J139">
-        <v>954</v>
+        <v>272</v>
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t xml:space="preserve">311544743</t>
+          <t xml:space="preserve">311645489</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t xml:space="preserve">Trykprøvning &amp; Energimærkning Danmark ApS</t>
+          <t xml:space="preserve">LKH Rådgivning</t>
         </is>
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-08-31</t>
+          <t xml:space="preserve">2032-11-28</t>
         </is>
       </c>
       <c r="N139" t="inlineStr">
@@ -10466,40 +10466,40 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ballerupvej 29</t>
+          <t xml:space="preserve">Nordtoftevej 56C</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t xml:space="preserve">3500</t>
+          <t xml:space="preserve">3520</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t xml:space="preserve">217538, 217539</t>
+          <t xml:space="preserve">2262618</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J140">
-        <v>704</v>
+        <v>420</v>
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t xml:space="preserve">311596730</t>
+          <t xml:space="preserve">311647626</t>
         </is>
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t xml:space="preserve">Domutech A/S</t>
+          <t xml:space="preserve">LKH Rådgivning</t>
         </is>
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-04-29</t>
+          <t xml:space="preserve">2032-12-07</t>
         </is>
       </c>
       <c r="N140" t="inlineStr">
@@ -10541,17 +10541,17 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skovgården 2A</t>
+          <t xml:space="preserve">Hvilebækgårdsvej 5</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t xml:space="preserve">3500</t>
+          <t xml:space="preserve">3520</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t xml:space="preserve">217474, 217475</t>
+          <t xml:space="preserve">8237461</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -10560,21 +10560,21 @@
         </is>
       </c>
       <c r="J141">
-        <v>316</v>
+        <v>560</v>
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t xml:space="preserve">311621249</t>
+          <t xml:space="preserve">311648223</t>
         </is>
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t xml:space="preserve">Domutech A/S</t>
+          <t xml:space="preserve">LKH Rådgivning</t>
         </is>
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-08-18</t>
+          <t xml:space="preserve">2032-12-09</t>
         </is>
       </c>
       <c r="N141" t="inlineStr">
@@ -10616,7 +10616,7 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lillevænget 1A</t>
+          <t xml:space="preserve">Stavnsholtvej 45</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
@@ -10626,30 +10626,30 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t xml:space="preserve">244717</t>
+          <t xml:space="preserve">8248420</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J142">
-        <v>1352</v>
+        <v>483</v>
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t xml:space="preserve">311626228</t>
+          <t xml:space="preserve">311649883</t>
         </is>
       </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t xml:space="preserve">Domutech A/S</t>
+          <t xml:space="preserve">LKH Rådgivning</t>
         </is>
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-09-07</t>
+          <t xml:space="preserve">2032-12-17</t>
         </is>
       </c>
       <c r="N142" t="inlineStr">
@@ -10691,7 +10691,7 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ryttergårdsvej 100</t>
+          <t xml:space="preserve">Stavnsholtvej 47</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
@@ -10701,30 +10701,30 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t xml:space="preserve">2263883</t>
+          <t xml:space="preserve">8248420</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J143">
-        <v>717</v>
+        <v>400</v>
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t xml:space="preserve">311631857</t>
+          <t xml:space="preserve">311649883</t>
         </is>
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dinraadgivning ApS</t>
+          <t xml:space="preserve">LKH Rådgivning</t>
         </is>
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-09-28</t>
+          <t xml:space="preserve">2032-12-17</t>
         </is>
       </c>
       <c r="N143" t="inlineStr">
@@ -10766,40 +10766,40 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t xml:space="preserve">Helikoptervej 7</t>
+          <t xml:space="preserve">Stavnsholtvej 49A</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t xml:space="preserve">3500</t>
+          <t xml:space="preserve">3520</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t xml:space="preserve">100352101</t>
+          <t xml:space="preserve">8248420</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t xml:space="preserve">413</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J144">
-        <v>467</v>
+        <v>400</v>
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t xml:space="preserve">311642385</t>
+          <t xml:space="preserve">311649883</t>
         </is>
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">LKH Rådgivning</t>
         </is>
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-11-14</t>
+          <t xml:space="preserve">2032-12-17</t>
         </is>
       </c>
       <c r="N144" t="inlineStr">
@@ -10841,7 +10841,7 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t xml:space="preserve">Farum Hovedgade 84</t>
+          <t xml:space="preserve">Stavnsholtvej 170A</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
@@ -10851,7 +10851,7 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t xml:space="preserve">2262452</t>
+          <t xml:space="preserve">2266026</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -10860,11 +10860,11 @@
         </is>
       </c>
       <c r="J145">
-        <v>475</v>
+        <v>439</v>
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t xml:space="preserve">311645153</t>
+          <t xml:space="preserve">311651924</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
@@ -10874,7 +10874,7 @@
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-11-25</t>
+          <t xml:space="preserve">2032-12-31</t>
         </is>
       </c>
       <c r="N145" t="inlineStr">
@@ -10916,7 +10916,7 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gammelgårdsvej 15</t>
+          <t xml:space="preserve">Stavnsholtvej 170A</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
@@ -10926,20 +10926,20 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t xml:space="preserve">2263023</t>
+          <t xml:space="preserve">2266026</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J146">
-        <v>288</v>
+        <v>331</v>
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t xml:space="preserve">311645147</t>
+          <t xml:space="preserve">311651924</t>
         </is>
       </c>
       <c r="L146" t="inlineStr">
@@ -10949,7 +10949,7 @@
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-11-25</t>
+          <t xml:space="preserve">2032-12-31</t>
         </is>
       </c>
       <c r="N146" t="inlineStr">
@@ -10991,30 +10991,30 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hvilebækgårdsvej 19</t>
+          <t xml:space="preserve">Ravnehusvej 20</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t xml:space="preserve">3520</t>
+          <t xml:space="preserve">3500</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t xml:space="preserve">2266425</t>
+          <t xml:space="preserve">2134248</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J147">
-        <v>531</v>
+        <v>774</v>
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t xml:space="preserve">311645148</t>
+          <t xml:space="preserve">311652067</t>
         </is>
       </c>
       <c r="L147" t="inlineStr">
@@ -11024,7 +11024,7 @@
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-11-25</t>
+          <t xml:space="preserve">2033-01-03</t>
         </is>
       </c>
       <c r="N147" t="inlineStr">
@@ -11066,17 +11066,17 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lindegårdsvej 2</t>
+          <t xml:space="preserve">Skovlinien 23</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t xml:space="preserve">3520</t>
+          <t xml:space="preserve">3500</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t xml:space="preserve">2262178</t>
+          <t xml:space="preserve">8736312</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -11085,11 +11085,11 @@
         </is>
       </c>
       <c r="J148">
-        <v>241</v>
+        <v>598</v>
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t xml:space="preserve">311645154</t>
+          <t xml:space="preserve">311652790</t>
         </is>
       </c>
       <c r="L148" t="inlineStr">
@@ -11099,7 +11099,7 @@
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-11-25</t>
+          <t xml:space="preserve">2033-01-06</t>
         </is>
       </c>
       <c r="N148" t="inlineStr">
@@ -11141,7 +11141,7 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hvilebækgårdsvej 15</t>
+          <t xml:space="preserve">Gammelgårdsvej 79</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
@@ -11151,30 +11151,30 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t xml:space="preserve">2266425</t>
+          <t xml:space="preserve">2263149</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J149">
-        <v>439</v>
+        <v>317</v>
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t xml:space="preserve">311645492</t>
+          <t xml:space="preserve">311654946</t>
         </is>
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t xml:space="preserve">LKH Rådgivning</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-11-28</t>
+          <t xml:space="preserve">2033-01-19</t>
         </is>
       </c>
       <c r="N149" t="inlineStr">
@@ -11216,30 +11216,30 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hvilebækgårdsvej 17</t>
+          <t xml:space="preserve">Perimetervejen 16</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t xml:space="preserve">3520</t>
+          <t xml:space="preserve">3500</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t xml:space="preserve">2266425</t>
+          <t xml:space="preserve">100177283</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">137</t>
         </is>
       </c>
       <c r="J150">
-        <v>372</v>
+        <v>1578</v>
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t xml:space="preserve">311645492</t>
+          <t xml:space="preserve">311655116</t>
         </is>
       </c>
       <c r="L150" t="inlineStr">
@@ -11249,7 +11249,7 @@
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-11-28</t>
+          <t xml:space="preserve">2033-01-19</t>
         </is>
       </c>
       <c r="N150" t="inlineStr">
@@ -11291,7 +11291,7 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nordtoftevej 56B</t>
+          <t xml:space="preserve">Stavnsholtvej 39</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
@@ -11301,7 +11301,7 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t xml:space="preserve">2262618</t>
+          <t xml:space="preserve">2266022</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -11310,11 +11310,11 @@
         </is>
       </c>
       <c r="J151">
-        <v>632</v>
+        <v>421</v>
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t xml:space="preserve">311645490</t>
+          <t xml:space="preserve">311655119</t>
         </is>
       </c>
       <c r="L151" t="inlineStr">
@@ -11324,7 +11324,7 @@
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-11-28</t>
+          <t xml:space="preserve">2033-01-19</t>
         </is>
       </c>
       <c r="N151" t="inlineStr">
@@ -11366,7 +11366,7 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stavnsholtvej 171</t>
+          <t xml:space="preserve">P E Rasmussensvej 3</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
@@ -11376,7 +11376,7 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t xml:space="preserve">8483113</t>
+          <t xml:space="preserve">2264486</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -11385,11 +11385,11 @@
         </is>
       </c>
       <c r="J152">
-        <v>272</v>
+        <v>99</v>
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t xml:space="preserve">311645489</t>
+          <t xml:space="preserve">311671198</t>
         </is>
       </c>
       <c r="L152" t="inlineStr">
@@ -11399,7 +11399,7 @@
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-11-28</t>
+          <t xml:space="preserve">2033-04-01</t>
         </is>
       </c>
       <c r="N152" t="inlineStr">
@@ -11441,7 +11441,7 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nordtoftevej 56C</t>
+          <t xml:space="preserve">Ryttergårdsvej 133</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
@@ -11451,20 +11451,20 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t xml:space="preserve">2262618</t>
+          <t xml:space="preserve">9523090</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J153">
-        <v>420</v>
+        <v>135</v>
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t xml:space="preserve">311647626</t>
+          <t xml:space="preserve">311671199</t>
         </is>
       </c>
       <c r="L153" t="inlineStr">
@@ -11474,7 +11474,7 @@
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-12-07</t>
+          <t xml:space="preserve">2033-04-01</t>
         </is>
       </c>
       <c r="N153" t="inlineStr">
@@ -11516,7 +11516,7 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hvilebækgårdsvej 5</t>
+          <t xml:space="preserve">Nordtoftevej 60</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
@@ -11526,20 +11526,20 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t xml:space="preserve">8237461</t>
+          <t xml:space="preserve">2262614</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J154">
-        <v>560</v>
+        <v>110</v>
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t xml:space="preserve">311648223</t>
+          <t xml:space="preserve">311682302</t>
         </is>
       </c>
       <c r="L154" t="inlineStr">
@@ -11549,7 +11549,7 @@
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-12-09</t>
+          <t xml:space="preserve">2033-05-23</t>
         </is>
       </c>
       <c r="N154" t="inlineStr">
@@ -11591,7 +11591,7 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stavnsholtvej 45</t>
+          <t xml:space="preserve">Stavnsholtvej 170B</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
@@ -11601,20 +11601,20 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t xml:space="preserve">8248420</t>
+          <t xml:space="preserve">8237160</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J155">
-        <v>483</v>
+        <v>531</v>
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t xml:space="preserve">311649883</t>
+          <t xml:space="preserve">311684200</t>
         </is>
       </c>
       <c r="L155" t="inlineStr">
@@ -11624,7 +11624,7 @@
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-12-17</t>
+          <t xml:space="preserve">2033-05-31</t>
         </is>
       </c>
       <c r="N155" t="inlineStr">
@@ -11666,7 +11666,7 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stavnsholtvej 47</t>
+          <t xml:space="preserve">Hvilebækgårdsvej 3B</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
@@ -11676,20 +11676,20 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t xml:space="preserve">8248420</t>
+          <t xml:space="preserve">7092630</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J156">
-        <v>400</v>
+        <v>2088</v>
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t xml:space="preserve">311649883</t>
+          <t xml:space="preserve">311686305</t>
         </is>
       </c>
       <c r="L156" t="inlineStr">
@@ -11699,7 +11699,7 @@
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-12-17</t>
+          <t xml:space="preserve">2033-06-08</t>
         </is>
       </c>
       <c r="N156" t="inlineStr">
@@ -11741,7 +11741,7 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stavnsholtvej 49A</t>
+          <t xml:space="preserve">Nordtoftevej 58</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
@@ -11751,20 +11751,20 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t xml:space="preserve">8248420</t>
+          <t xml:space="preserve">2262614</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J157">
-        <v>400</v>
+        <v>7430</v>
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t xml:space="preserve">311649883</t>
+          <t xml:space="preserve">311686309</t>
         </is>
       </c>
       <c r="L157" t="inlineStr">
@@ -11774,7 +11774,7 @@
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-12-17</t>
+          <t xml:space="preserve">2033-06-08</t>
         </is>
       </c>
       <c r="N157" t="inlineStr">
@@ -11816,7 +11816,7 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stavnsholtvej 170A</t>
+          <t xml:space="preserve">Nordtoftevej 58</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
@@ -11826,20 +11826,20 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t xml:space="preserve">2266026</t>
+          <t xml:space="preserve">2262614</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J158">
-        <v>439</v>
+        <v>2417</v>
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t xml:space="preserve">311651924</t>
+          <t xml:space="preserve">311686308</t>
         </is>
       </c>
       <c r="L158" t="inlineStr">
@@ -11849,7 +11849,7 @@
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-12-31</t>
+          <t xml:space="preserve">2033-06-08</t>
         </is>
       </c>
       <c r="N158" t="inlineStr">
@@ -11891,30 +11891,30 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stavnsholtvej 170A</t>
+          <t xml:space="preserve">Poppel Alle 6</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t xml:space="preserve">3520</t>
+          <t xml:space="preserve">3500</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t xml:space="preserve">2266026</t>
+          <t xml:space="preserve">8736223</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">23</t>
         </is>
       </c>
       <c r="J159">
-        <v>331</v>
+        <v>591</v>
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t xml:space="preserve">311651924</t>
+          <t xml:space="preserve">311753515</t>
         </is>
       </c>
       <c r="L159" t="inlineStr">
@@ -11924,7 +11924,7 @@
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-12-31</t>
+          <t xml:space="preserve">2034-04-21</t>
         </is>
       </c>
       <c r="N159" t="inlineStr">
@@ -11966,7 +11966,7 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ravnehusvej 20</t>
+          <t xml:space="preserve">Ryetvej 15</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
@@ -11976,20 +11976,20 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t xml:space="preserve">2134248</t>
+          <t xml:space="preserve">2136642</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J160">
-        <v>774</v>
+        <v>96</v>
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t xml:space="preserve">311652067</t>
+          <t xml:space="preserve">311753519</t>
         </is>
       </c>
       <c r="L160" t="inlineStr">
@@ -11999,7 +11999,7 @@
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-01-03</t>
+          <t xml:space="preserve">2034-04-21</t>
         </is>
       </c>
       <c r="N160" t="inlineStr">
@@ -12041,7 +12041,7 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skovlinien 23</t>
+          <t xml:space="preserve">Sandet 77</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
@@ -12051,20 +12051,20 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t xml:space="preserve">8736312</t>
+          <t xml:space="preserve">8736260</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">77</t>
         </is>
       </c>
       <c r="J161">
-        <v>598</v>
+        <v>315</v>
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t xml:space="preserve">311652790</t>
+          <t xml:space="preserve">311753517</t>
         </is>
       </c>
       <c r="L161" t="inlineStr">
@@ -12074,7 +12074,7 @@
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-01-06</t>
+          <t xml:space="preserve">2034-04-21</t>
         </is>
       </c>
       <c r="N161" t="inlineStr">
@@ -12116,40 +12116,40 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gammelgårdsvej 79</t>
+          <t xml:space="preserve">Solbjerghaven 6</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t xml:space="preserve">3520</t>
+          <t xml:space="preserve">3500</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t xml:space="preserve">2263149</t>
+          <t xml:space="preserve">8234923</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J162">
-        <v>317</v>
+        <v>1571</v>
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t xml:space="preserve">311654946</t>
+          <t xml:space="preserve">311753516</t>
         </is>
       </c>
       <c r="L162" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">LKH Rådgivning</t>
         </is>
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-01-19</t>
+          <t xml:space="preserve">2034-04-21</t>
         </is>
       </c>
       <c r="N162" t="inlineStr">
@@ -12191,30 +12191,30 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t xml:space="preserve">Perimetervejen 16</t>
+          <t xml:space="preserve">Paltholmterrasserne 1</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t xml:space="preserve">3500</t>
+          <t xml:space="preserve">3520</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t xml:space="preserve">100177283</t>
+          <t xml:space="preserve">2263549</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t xml:space="preserve">137</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J163">
-        <v>1578</v>
+        <v>10848</v>
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t xml:space="preserve">311655116</t>
+          <t xml:space="preserve">311788248</t>
         </is>
       </c>
       <c r="L163" t="inlineStr">
@@ -12224,7 +12224,7 @@
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-01-19</t>
+          <t xml:space="preserve">2034-09-30</t>
         </is>
       </c>
       <c r="N163" t="inlineStr">
@@ -12266,7 +12266,7 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stavnsholtvej 39</t>
+          <t xml:space="preserve">Stavnsholtvej 43F</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
@@ -12276,7 +12276,7 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t xml:space="preserve">2266022</t>
+          <t xml:space="preserve">8248420</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -12285,21 +12285,21 @@
         </is>
       </c>
       <c r="J164">
-        <v>421</v>
+        <v>352</v>
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t xml:space="preserve">311655119</t>
+          <t xml:space="preserve">311818719</t>
         </is>
       </c>
       <c r="L164" t="inlineStr">
         <is>
-          <t xml:space="preserve">LKH Rådgivning</t>
+          <t xml:space="preserve">Jysk Trykprøvning A/S</t>
         </is>
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-01-19</t>
+          <t xml:space="preserve">2035-03-19</t>
         </is>
       </c>
       <c r="N164" t="inlineStr">
@@ -12341,17 +12341,17 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t xml:space="preserve">P E Rasmussensvej 3</t>
+          <t xml:space="preserve">Bavnehøj Park 4A</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t xml:space="preserve">3520</t>
+          <t xml:space="preserve">3500</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t xml:space="preserve">2264486</t>
+          <t xml:space="preserve">2137259</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -12360,11 +12360,11 @@
         </is>
       </c>
       <c r="J165">
-        <v>99</v>
+        <v>715</v>
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t xml:space="preserve">311671198</t>
+          <t xml:space="preserve">311896963</t>
         </is>
       </c>
       <c r="L165" t="inlineStr">
@@ -12374,7 +12374,7 @@
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-04-01</t>
+          <t xml:space="preserve">2036-04-27</t>
         </is>
       </c>
       <c r="N165" t="inlineStr">
@@ -12416,17 +12416,17 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ryttergårdsvej 133</t>
+          <t xml:space="preserve">Bygaden 27</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t xml:space="preserve">3520</t>
+          <t xml:space="preserve">3500</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t xml:space="preserve">9523090</t>
+          <t xml:space="preserve">2135316</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -12435,11 +12435,11 @@
         </is>
       </c>
       <c r="J166">
-        <v>135</v>
+        <v>363</v>
       </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t xml:space="preserve">311671199</t>
+          <t xml:space="preserve">311896964</t>
         </is>
       </c>
       <c r="L166" t="inlineStr">
@@ -12449,7 +12449,7 @@
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-04-01</t>
+          <t xml:space="preserve">2036-04-27</t>
         </is>
       </c>
       <c r="N166" t="inlineStr">
@@ -12491,30 +12491,30 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nordtoftevej 60</t>
+          <t xml:space="preserve">Bygaden 29</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t xml:space="preserve">3520</t>
+          <t xml:space="preserve">3500</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t xml:space="preserve">2262614</t>
+          <t xml:space="preserve">2135316</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J167">
-        <v>110</v>
+        <v>141</v>
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t xml:space="preserve">311682302</t>
+          <t xml:space="preserve">311896964</t>
         </is>
       </c>
       <c r="L167" t="inlineStr">
@@ -12524,7 +12524,7 @@
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-05-23</t>
+          <t xml:space="preserve">2036-04-27</t>
         </is>
       </c>
       <c r="N167" t="inlineStr">
@@ -12566,30 +12566,30 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stavnsholtvej 170B</t>
+          <t xml:space="preserve">Bygaden 29</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t xml:space="preserve">3520</t>
+          <t xml:space="preserve">3500</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t xml:space="preserve">8237160</t>
+          <t xml:space="preserve">2135316</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J168">
-        <v>531</v>
+        <v>98</v>
       </c>
       <c r="K168" t="inlineStr">
         <is>
-          <t xml:space="preserve">311684200</t>
+          <t xml:space="preserve">311896964</t>
         </is>
       </c>
       <c r="L168" t="inlineStr">
@@ -12599,7 +12599,7 @@
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-05-31</t>
+          <t xml:space="preserve">2036-04-27</t>
         </is>
       </c>
       <c r="N168" t="inlineStr">
@@ -12641,7 +12641,7 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hvilebækgårdsvej 3B</t>
+          <t xml:space="preserve">Farum Park 2A</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
@@ -12651,7 +12651,7 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t xml:space="preserve">7092630</t>
+          <t xml:space="preserve">8794316</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -12660,11 +12660,11 @@
         </is>
       </c>
       <c r="J169">
-        <v>2088</v>
+        <v>6776</v>
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t xml:space="preserve">311686305</t>
+          <t xml:space="preserve">311896965</t>
         </is>
       </c>
       <c r="L169" t="inlineStr">
@@ -12674,7 +12674,7 @@
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-06-08</t>
+          <t xml:space="preserve">2036-04-27</t>
         </is>
       </c>
       <c r="N169" t="inlineStr">
@@ -12716,17 +12716,17 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nordtoftevej 58</t>
+          <t xml:space="preserve">Ryetvej 157</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t xml:space="preserve">3520</t>
+          <t xml:space="preserve">3500</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t xml:space="preserve">2262614</t>
+          <t xml:space="preserve">2136644</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -12735,11 +12735,11 @@
         </is>
       </c>
       <c r="J170">
-        <v>7430</v>
+        <v>692</v>
       </c>
       <c r="K170" t="inlineStr">
         <is>
-          <t xml:space="preserve">311686309</t>
+          <t xml:space="preserve">311896966</t>
         </is>
       </c>
       <c r="L170" t="inlineStr">
@@ -12749,7 +12749,7 @@
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-06-08</t>
+          <t xml:space="preserve">2036-04-27</t>
         </is>
       </c>
       <c r="N170" t="inlineStr">
@@ -12791,30 +12791,30 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nordtoftevej 58</t>
+          <t xml:space="preserve">Solbjerghaven 2</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t xml:space="preserve">3520</t>
+          <t xml:space="preserve">3500</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t xml:space="preserve">2262614</t>
+          <t xml:space="preserve">8234924</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J171">
-        <v>2417</v>
+        <v>836</v>
       </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t xml:space="preserve">311686308</t>
+          <t xml:space="preserve">311896969</t>
         </is>
       </c>
       <c r="L171" t="inlineStr">
@@ -12824,7 +12824,7 @@
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-06-08</t>
+          <t xml:space="preserve">2036-04-27</t>
         </is>
       </c>
       <c r="N171" t="inlineStr">
@@ -12866,7 +12866,7 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Poppel Alle 6</t>
+          <t xml:space="preserve">Månedalstien 8</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
@@ -12876,20 +12876,20 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t xml:space="preserve">8736223</t>
+          <t xml:space="preserve">2134115</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t xml:space="preserve">23</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J172">
-        <v>591</v>
+        <v>2027</v>
       </c>
       <c r="K172" t="inlineStr">
         <is>
-          <t xml:space="preserve">311753515</t>
+          <t xml:space="preserve">311908909</t>
         </is>
       </c>
       <c r="L172" t="inlineStr">
@@ -12899,7 +12899,7 @@
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-04-21</t>
+          <t xml:space="preserve">2036-06-17</t>
         </is>
       </c>
       <c r="N172" t="inlineStr">
@@ -12941,7 +12941,7 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ryetvej 15</t>
+          <t xml:space="preserve">Ryetvej 17A</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
@@ -12956,15 +12956,15 @@
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J173">
-        <v>96</v>
+        <v>168</v>
       </c>
       <c r="K173" t="inlineStr">
         <is>
-          <t xml:space="preserve">311753519</t>
+          <t xml:space="preserve">311908907</t>
         </is>
       </c>
       <c r="L173" t="inlineStr">
@@ -12974,7 +12974,7 @@
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-04-21</t>
+          <t xml:space="preserve">2036-06-17</t>
         </is>
       </c>
       <c r="N173" t="inlineStr">
@@ -13016,7 +13016,7 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sandet 77</t>
+          <t xml:space="preserve">Ryetvej 17B</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
@@ -13026,20 +13026,20 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t xml:space="preserve">8736260</t>
+          <t xml:space="preserve">2136642</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t xml:space="preserve">77</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J174">
-        <v>315</v>
+        <v>228</v>
       </c>
       <c r="K174" t="inlineStr">
         <is>
-          <t xml:space="preserve">311753517</t>
+          <t xml:space="preserve">311908907</t>
         </is>
       </c>
       <c r="L174" t="inlineStr">
@@ -13049,7 +13049,7 @@
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-04-21</t>
+          <t xml:space="preserve">2036-06-17</t>
         </is>
       </c>
       <c r="N174" t="inlineStr">
@@ -13091,30 +13091,30 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t xml:space="preserve">Solbjerghaven 6</t>
+          <t xml:space="preserve">Ryttergårdsvej 106</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t xml:space="preserve">3500</t>
+          <t xml:space="preserve">3520</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t xml:space="preserve">8234923</t>
+          <t xml:space="preserve">8794315</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J175">
-        <v>1571</v>
+        <v>586</v>
       </c>
       <c r="K175" t="inlineStr">
         <is>
-          <t xml:space="preserve">311753516</t>
+          <t xml:space="preserve">311908908</t>
         </is>
       </c>
       <c r="L175" t="inlineStr">
@@ -13124,7 +13124,7 @@
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-04-21</t>
+          <t xml:space="preserve">2036-06-17</t>
         </is>
       </c>
       <c r="N175" t="inlineStr">
@@ -13166,30 +13166,30 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stavnsholtvej 177</t>
+          <t xml:space="preserve">Bringetoften 26</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t xml:space="preserve">3520</t>
+          <t xml:space="preserve">3500</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t xml:space="preserve">9046646</t>
+          <t xml:space="preserve">2132753</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J176">
-        <v>140</v>
+        <v>838</v>
       </c>
       <c r="K176" t="inlineStr">
         <is>
-          <t xml:space="preserve">311753518</t>
+          <t xml:space="preserve">311918258</t>
         </is>
       </c>
       <c r="L176" t="inlineStr">
@@ -13199,7 +13199,7 @@
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-04-21</t>
+          <t xml:space="preserve">2036-08-10</t>
         </is>
       </c>
       <c r="N176" t="inlineStr">
@@ -13241,7 +13241,7 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t xml:space="preserve">Paltholmterrasserne 1</t>
+          <t xml:space="preserve">Farum Park 18</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
@@ -13251,7 +13251,7 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t xml:space="preserve">2263549</t>
+          <t xml:space="preserve">7135495</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
@@ -13260,11 +13260,11 @@
         </is>
       </c>
       <c r="J177">
-        <v>10848</v>
+        <v>5564</v>
       </c>
       <c r="K177" t="inlineStr">
         <is>
-          <t xml:space="preserve">311788248</t>
+          <t xml:space="preserve">311918261</t>
         </is>
       </c>
       <c r="L177" t="inlineStr">
@@ -13274,7 +13274,7 @@
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-09-30</t>
+          <t xml:space="preserve">2036-08-10</t>
         </is>
       </c>
       <c r="N177" t="inlineStr">
@@ -13316,7 +13316,7 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stavnsholtvej 43F</t>
+          <t xml:space="preserve">Farumgårds Alle 32</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
@@ -13326,7 +13326,7 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t xml:space="preserve">8248420</t>
+          <t xml:space="preserve">2264883</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
@@ -13335,21 +13335,21 @@
         </is>
       </c>
       <c r="J178">
-        <v>352</v>
+        <v>68</v>
       </c>
       <c r="K178" t="inlineStr">
         <is>
-          <t xml:space="preserve">311818719</t>
+          <t xml:space="preserve">311918259</t>
         </is>
       </c>
       <c r="L178" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jysk Trykprøvning A/S</t>
+          <t xml:space="preserve">LKH Rådgivning</t>
         </is>
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-03-19</t>
+          <t xml:space="preserve">2036-08-10</t>
         </is>
       </c>
       <c r="N178" t="inlineStr">
@@ -13391,7 +13391,7 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bavnehøj Park 4A</t>
+          <t xml:space="preserve">Ny Vestergårdsvej 9</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
@@ -13401,20 +13401,20 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t xml:space="preserve">2137259</t>
+          <t xml:space="preserve">2135988</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J179">
-        <v>715</v>
+        <v>424</v>
       </c>
       <c r="K179" t="inlineStr">
         <is>
-          <t xml:space="preserve">311896963</t>
+          <t xml:space="preserve">311918268</t>
         </is>
       </c>
       <c r="L179" t="inlineStr">
@@ -13424,7 +13424,7 @@
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-04-27</t>
+          <t xml:space="preserve">2036-08-10</t>
         </is>
       </c>
       <c r="N179" t="inlineStr">
@@ -13466,30 +13466,30 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bygaden 27</t>
+          <t xml:space="preserve">Ryttergårdsvej 135</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t xml:space="preserve">3500</t>
+          <t xml:space="preserve">3520</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t xml:space="preserve">2135316</t>
+          <t xml:space="preserve">8396261</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J180">
-        <v>363</v>
+        <v>586</v>
       </c>
       <c r="K180" t="inlineStr">
         <is>
-          <t xml:space="preserve">311896964</t>
+          <t xml:space="preserve">311918265</t>
         </is>
       </c>
       <c r="L180" t="inlineStr">
@@ -13499,7 +13499,7 @@
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-04-27</t>
+          <t xml:space="preserve">2036-08-10</t>
         </is>
       </c>
       <c r="N180" t="inlineStr">
@@ -13541,7 +13541,7 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bygaden 29</t>
+          <t xml:space="preserve">Sandet 2</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
@@ -13551,20 +13551,20 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t xml:space="preserve">2135316</t>
+          <t xml:space="preserve">2135245</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J181">
-        <v>141</v>
+        <v>123</v>
       </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t xml:space="preserve">311896964</t>
+          <t xml:space="preserve">311918270</t>
         </is>
       </c>
       <c r="L181" t="inlineStr">
@@ -13574,7 +13574,7 @@
       </c>
       <c r="M181" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-04-27</t>
+          <t xml:space="preserve">2036-08-10</t>
         </is>
       </c>
       <c r="N181" t="inlineStr">
@@ -13616,7 +13616,7 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bygaden 29</t>
+          <t xml:space="preserve">Søvej 18</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
@@ -13626,20 +13626,20 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t xml:space="preserve">2135316</t>
+          <t xml:space="preserve">2135926</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J182">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="K182" t="inlineStr">
         <is>
-          <t xml:space="preserve">311896964</t>
+          <t xml:space="preserve">311918272</t>
         </is>
       </c>
       <c r="L182" t="inlineStr">
@@ -13649,7 +13649,7 @@
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-04-27</t>
+          <t xml:space="preserve">2036-08-10</t>
         </is>
       </c>
       <c r="N182" t="inlineStr">
@@ -13691,30 +13691,30 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t xml:space="preserve">Farum Park 2A</t>
+          <t xml:space="preserve">Søvej 18</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t xml:space="preserve">3520</t>
+          <t xml:space="preserve">3500</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t xml:space="preserve">8794316</t>
+          <t xml:space="preserve">2135926</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J183">
-        <v>6776</v>
+        <v>65</v>
       </c>
       <c r="K183" t="inlineStr">
         <is>
-          <t xml:space="preserve">311896965</t>
+          <t xml:space="preserve">311918272</t>
         </is>
       </c>
       <c r="L183" t="inlineStr">
@@ -13724,7 +13724,7 @@
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-04-27</t>
+          <t xml:space="preserve">2036-08-10</t>
         </is>
       </c>
       <c r="N183" t="inlineStr">
@@ -13766,17 +13766,17 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ryetvej 157</t>
+          <t xml:space="preserve">V M Amdrupvej 17</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t xml:space="preserve">3500</t>
+          <t xml:space="preserve">3520</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t xml:space="preserve">2136644</t>
+          <t xml:space="preserve">2264767</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -13785,11 +13785,11 @@
         </is>
       </c>
       <c r="J184">
-        <v>692</v>
+        <v>138</v>
       </c>
       <c r="K184" t="inlineStr">
         <is>
-          <t xml:space="preserve">311896966</t>
+          <t xml:space="preserve">311918256</t>
         </is>
       </c>
       <c r="L184" t="inlineStr">
@@ -13799,7 +13799,7 @@
       </c>
       <c r="M184" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-04-27</t>
+          <t xml:space="preserve">2036-08-10</t>
         </is>
       </c>
       <c r="N184" t="inlineStr">
@@ -13841,7 +13841,7 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t xml:space="preserve">Solbjerghaven 2</t>
+          <t xml:space="preserve">Ballerupvej 60</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
@@ -13851,7 +13851,7 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t xml:space="preserve">8234924</t>
+          <t xml:space="preserve">2138713</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
@@ -13860,11 +13860,11 @@
         </is>
       </c>
       <c r="J185">
-        <v>836</v>
+        <v>475</v>
       </c>
       <c r="K185" t="inlineStr">
         <is>
-          <t xml:space="preserve">311896969</t>
+          <t xml:space="preserve">311926967</t>
         </is>
       </c>
       <c r="L185" t="inlineStr">
@@ -13874,7 +13874,7 @@
       </c>
       <c r="M185" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-04-27</t>
+          <t xml:space="preserve">2036-09-21</t>
         </is>
       </c>
       <c r="N185" t="inlineStr">
@@ -13916,7 +13916,7 @@
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t xml:space="preserve">Månedalstien 8</t>
+          <t xml:space="preserve">Kirke Værløsevej 62</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
@@ -13926,7 +13926,7 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t xml:space="preserve">2134115</t>
+          <t xml:space="preserve">8736262</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
@@ -13935,11 +13935,11 @@
         </is>
       </c>
       <c r="J186">
-        <v>2027</v>
+        <v>213</v>
       </c>
       <c r="K186" t="inlineStr">
         <is>
-          <t xml:space="preserve">311908909</t>
+          <t xml:space="preserve">311926981</t>
         </is>
       </c>
       <c r="L186" t="inlineStr">
@@ -13949,7 +13949,7 @@
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-06-17</t>
+          <t xml:space="preserve">2036-09-21</t>
         </is>
       </c>
       <c r="N186" t="inlineStr">
@@ -13991,7 +13991,7 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ryetvej 17A</t>
+          <t xml:space="preserve">Kirke Værløsevej 62</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
@@ -14001,20 +14001,20 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t xml:space="preserve">2136642</t>
+          <t xml:space="preserve">8736262</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J187">
-        <v>168</v>
+        <v>356</v>
       </c>
       <c r="K187" t="inlineStr">
         <is>
-          <t xml:space="preserve">311908907</t>
+          <t xml:space="preserve">311926980</t>
         </is>
       </c>
       <c r="L187" t="inlineStr">
@@ -14024,7 +14024,7 @@
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-06-17</t>
+          <t xml:space="preserve">2036-09-21</t>
         </is>
       </c>
       <c r="N187" t="inlineStr">
@@ -14066,7 +14066,7 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ryetvej 17B</t>
+          <t xml:space="preserve">Kirke Værløsevej 62</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
@@ -14076,20 +14076,20 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t xml:space="preserve">2136642</t>
+          <t xml:space="preserve">8736262</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J188">
-        <v>228</v>
+        <v>293</v>
       </c>
       <c r="K188" t="inlineStr">
         <is>
-          <t xml:space="preserve">311908907</t>
+          <t xml:space="preserve">311926981</t>
         </is>
       </c>
       <c r="L188" t="inlineStr">
@@ -14099,7 +14099,7 @@
       </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-06-17</t>
+          <t xml:space="preserve">2036-09-21</t>
         </is>
       </c>
       <c r="N188" t="inlineStr">
@@ -14141,30 +14141,30 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ryttergårdsvej 106</t>
+          <t xml:space="preserve">Kirke Værløsevej 62</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t xml:space="preserve">3520</t>
+          <t xml:space="preserve">3500</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t xml:space="preserve">8794315</t>
+          <t xml:space="preserve">8736262</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J189">
-        <v>586</v>
+        <v>245</v>
       </c>
       <c r="K189" t="inlineStr">
         <is>
-          <t xml:space="preserve">311908908</t>
+          <t xml:space="preserve">311926981</t>
         </is>
       </c>
       <c r="L189" t="inlineStr">
@@ -14174,7 +14174,7 @@
       </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-06-17</t>
+          <t xml:space="preserve">2036-09-21</t>
         </is>
       </c>
       <c r="N189" t="inlineStr">
@@ -14216,7 +14216,7 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bringetoften 26</t>
+          <t xml:space="preserve">Skandrups Alle 7</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
@@ -14226,7 +14226,7 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t xml:space="preserve">2132753</t>
+          <t xml:space="preserve">2134015</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
@@ -14235,11 +14235,11 @@
         </is>
       </c>
       <c r="J190">
-        <v>838</v>
+        <v>324</v>
       </c>
       <c r="K190" t="inlineStr">
         <is>
-          <t xml:space="preserve">311918258</t>
+          <t xml:space="preserve">311926972</t>
         </is>
       </c>
       <c r="L190" t="inlineStr">
@@ -14249,7 +14249,7 @@
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-08-10</t>
+          <t xml:space="preserve">2036-09-21</t>
         </is>
       </c>
       <c r="N190" t="inlineStr">
@@ -14291,7 +14291,7 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t xml:space="preserve">Farum Park 18</t>
+          <t xml:space="preserve">Stavnsholtvej 168</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
@@ -14301,20 +14301,20 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t xml:space="preserve">7135495</t>
+          <t xml:space="preserve">2266105</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J191">
-        <v>5564</v>
+        <v>867</v>
       </c>
       <c r="K191" t="inlineStr">
         <is>
-          <t xml:space="preserve">311918261</t>
+          <t xml:space="preserve">311926968</t>
         </is>
       </c>
       <c r="L191" t="inlineStr">
@@ -14324,7 +14324,7 @@
       </c>
       <c r="M191" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-08-10</t>
+          <t xml:space="preserve">2036-09-21</t>
         </is>
       </c>
       <c r="N191" t="inlineStr">
@@ -14366,7 +14366,7 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t xml:space="preserve">Farumgårds Alle 32</t>
+          <t xml:space="preserve">Stavnsholtvej 171A</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
@@ -14376,7 +14376,7 @@
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t xml:space="preserve">2264883</t>
+          <t xml:space="preserve">8483114</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
@@ -14385,11 +14385,11 @@
         </is>
       </c>
       <c r="J192">
-        <v>68</v>
+        <v>542</v>
       </c>
       <c r="K192" t="inlineStr">
         <is>
-          <t xml:space="preserve">311918259</t>
+          <t xml:space="preserve">311926975</t>
         </is>
       </c>
       <c r="L192" t="inlineStr">
@@ -14399,7 +14399,7 @@
       </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-08-10</t>
+          <t xml:space="preserve">2036-09-21</t>
         </is>
       </c>
       <c r="N192" t="inlineStr">
@@ -14441,30 +14441,30 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ny Vestergårdsvej 9</t>
+          <t xml:space="preserve">Stavnsholtvej 177</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t xml:space="preserve">3500</t>
+          <t xml:space="preserve">3520</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t xml:space="preserve">2135988</t>
+          <t xml:space="preserve">9046646</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J193">
-        <v>424</v>
+        <v>253</v>
       </c>
       <c r="K193" t="inlineStr">
         <is>
-          <t xml:space="preserve">311918268</t>
+          <t xml:space="preserve">311926979</t>
         </is>
       </c>
       <c r="L193" t="inlineStr">
@@ -14474,7 +14474,7 @@
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-08-10</t>
+          <t xml:space="preserve">2036-09-21</t>
         </is>
       </c>
       <c r="N193" t="inlineStr">
@@ -14516,7 +14516,7 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ryttergårdsvej 135</t>
+          <t xml:space="preserve">Stavnsholtvej 177</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
@@ -14526,20 +14526,20 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t xml:space="preserve">8396261</t>
+          <t xml:space="preserve">9046646</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J194">
-        <v>586</v>
+        <v>140</v>
       </c>
       <c r="K194" t="inlineStr">
         <is>
-          <t xml:space="preserve">311918265</t>
+          <t xml:space="preserve">311926976</t>
         </is>
       </c>
       <c r="L194" t="inlineStr">
@@ -14549,7 +14549,7 @@
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-08-10</t>
+          <t xml:space="preserve">2036-09-21</t>
         </is>
       </c>
       <c r="N194" t="inlineStr">
@@ -14591,17 +14591,17 @@
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sandet 2</t>
+          <t xml:space="preserve">Stavnsholtvej 180</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t xml:space="preserve">3500</t>
+          <t xml:space="preserve">3520</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t xml:space="preserve">2135245</t>
+          <t xml:space="preserve">2266105</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
@@ -14610,11 +14610,11 @@
         </is>
       </c>
       <c r="J195">
-        <v>123</v>
+        <v>309</v>
       </c>
       <c r="K195" t="inlineStr">
         <is>
-          <t xml:space="preserve">311918270</t>
+          <t xml:space="preserve">311926969</t>
         </is>
       </c>
       <c r="L195" t="inlineStr">
@@ -14624,7 +14624,7 @@
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-08-10</t>
+          <t xml:space="preserve">2036-09-21</t>
         </is>
       </c>
       <c r="N195" t="inlineStr">
@@ -14666,30 +14666,30 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søvej 18</t>
+          <t xml:space="preserve">Stavnsholtvej 41</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t xml:space="preserve">3500</t>
+          <t xml:space="preserve">3520</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t xml:space="preserve">2135926</t>
+          <t xml:space="preserve">7966736</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J196">
-        <v>102</v>
+        <v>3594</v>
       </c>
       <c r="K196" t="inlineStr">
         <is>
-          <t xml:space="preserve">311918272</t>
+          <t xml:space="preserve">311926970</t>
         </is>
       </c>
       <c r="L196" t="inlineStr">
@@ -14699,7 +14699,7 @@
       </c>
       <c r="M196" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-08-10</t>
+          <t xml:space="preserve">2036-09-21</t>
         </is>
       </c>
       <c r="N196" t="inlineStr">
@@ -14741,30 +14741,30 @@
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søvej 18</t>
+          <t xml:space="preserve">Stavnsholtvej 41</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t xml:space="preserve">3500</t>
+          <t xml:space="preserve">3520</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t xml:space="preserve">2135926</t>
+          <t xml:space="preserve">7966736</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J197">
-        <v>65</v>
+        <v>6415</v>
       </c>
       <c r="K197" t="inlineStr">
         <is>
-          <t xml:space="preserve">311918272</t>
+          <t xml:space="preserve">311926971</t>
         </is>
       </c>
       <c r="L197" t="inlineStr">
@@ -14774,7 +14774,7 @@
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-08-10</t>
+          <t xml:space="preserve">2036-09-21</t>
         </is>
       </c>
       <c r="N197" t="inlineStr">
@@ -14816,17 +14816,17 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t xml:space="preserve">V M Amdrupvej 17</t>
+          <t xml:space="preserve">Storkekrogen 2</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t xml:space="preserve">3520</t>
+          <t xml:space="preserve">3500</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t xml:space="preserve">2264767</t>
+          <t xml:space="preserve">2134919</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
@@ -14835,11 +14835,11 @@
         </is>
       </c>
       <c r="J198">
-        <v>138</v>
+        <v>334</v>
       </c>
       <c r="K198" t="inlineStr">
         <is>
-          <t xml:space="preserve">311918256</t>
+          <t xml:space="preserve">311926974</t>
         </is>
       </c>
       <c r="L198" t="inlineStr">
@@ -14849,7 +14849,7 @@
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-08-10</t>
+          <t xml:space="preserve">2036-09-21</t>
         </is>
       </c>
       <c r="N198" t="inlineStr">

--- a/public/exports-from-60/29188327.xlsx
+++ b/public/exports-from-60/29188327.xlsx
@@ -14464,7 +14464,7 @@
       </c>
       <c r="K193" t="inlineStr">
         <is>
-          <t xml:space="preserve">311926979</t>
+          <t xml:space="preserve">311926976</t>
         </is>
       </c>
       <c r="L193" t="inlineStr">
